--- a/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>BA</t>
   </si>
@@ -656,399 +656,411 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22018000</v>
+      </c>
+      <c r="E8" s="3">
         <v>18104000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>19751000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17921000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19980000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15956000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16681000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13991000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14793000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15278000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16998000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15217000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15802000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14139000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11807000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16908000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>20560000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>19980000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>21361000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>22917000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>28341000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>25146000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>24258000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>23382000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>24770000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>24223000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>23051000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>21961000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>23286000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>23898000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>19321000</v>
+      </c>
+      <c r="E9" s="3">
         <v>16939000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>17812000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15998000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18124000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16778000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14559000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13645000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17307000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13566000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14588000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13808000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>20992000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13105000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12978000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16768000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18708000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16930000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>17810000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>18645000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>22090000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>21040000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>19536000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>18824000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>19881000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>19956000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>18702000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>18073000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>19464000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>19904000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2697000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1165000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1939000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1923000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1856000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-822000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2122000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>346000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-2514000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1712000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2410000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1409000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-5190000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1034000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-1171000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>140000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1852000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3050000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3551000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4272000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6251000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4106000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4722000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4558000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4889000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4267000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4349000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3888000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3822000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3994000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1081,100 +1093,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>881000</v>
+      </c>
+      <c r="E12" s="3">
         <v>958000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>797000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>741000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>794000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>727000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>698000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>633000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>678000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>575000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>497000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>499000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>605000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>574000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>625000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>672000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>749000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>778000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>826000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>866000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>852000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>826000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>827000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>764000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>762000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>768000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>813000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>836000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>726000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>857000</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1265,8 +1281,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1303,11 +1322,11 @@
       <c r="N14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P14" s="3">
         <v>498000</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>24</v>
@@ -1315,17 +1334,17 @@
       <c r="R14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T14" s="3">
         <v>2649000</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>5610000</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>24</v>
@@ -1336,8 +1355,8 @@
       <c r="Y14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1357,8 +1376,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1449,8 +1471,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1480,192 +1505,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>21735000</v>
+      </c>
+      <c r="E17" s="3">
         <v>18912000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19850000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18070000</v>
       </c>
-      <c r="G17" s="3">
-        <v>20333000</v>
-      </c>
       <c r="H17" s="3">
+        <v>20325000</v>
+      </c>
+      <c r="I17" s="3">
         <v>18748000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15901000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15153000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18964000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14949000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15975000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15300000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23851000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14540000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14771000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18261000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22764000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18721000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>24741000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>20567000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>24166000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22919000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>21548000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>20507000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>21792000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>21593000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>20521000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>19755000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21103000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>21616000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-808000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-99000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-149000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-353000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-345000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-2792000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>780000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1162000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4171000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>329000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1023000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-83000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8049000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-401000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2964000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1353000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2204000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1259000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3380000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2350000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4175000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2227000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2710000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2875000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2978000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2630000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2530000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2206000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2183000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2282000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1698,468 +1730,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>308000</v>
+      </c>
+      <c r="E20" s="3">
         <v>297000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>320000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>302000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>336000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>288000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>253000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>181000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>132000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>30000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>199000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>190000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>122000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>119000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>94000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>112000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>104000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>121000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>107000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>106000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>29000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>12000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>66000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>32000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>40000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>25000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>26000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1072000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-44000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>677000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>610000</v>
       </c>
-      <c r="G21" s="3">
-        <v>485000</v>
-      </c>
       <c r="H21" s="3">
+        <v>493000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-2011000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1531000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-495000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3505000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>882000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1773000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>643000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7349000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>283000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2323000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-685000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1472000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1956000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2727000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2977000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4787000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2762000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3202000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3442000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3587000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3184000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3043000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2700000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2728000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2758000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>600000</v>
+      </c>
+      <c r="E22" s="3">
         <v>589000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>621000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>649000</v>
       </c>
-      <c r="G22" s="3">
-        <v>632000</v>
-      </c>
       <c r="H22" s="3">
+        <v>640000</v>
+      </c>
+      <c r="I22" s="3">
         <v>628000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>656000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>637000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>661000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>669000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>673000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>679000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>698000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>643000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>553000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>262000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>242000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>203000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>154000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>123000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>158000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>106000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>109000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>102000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>93000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>87000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>93000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>87000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>79000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1100000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-400000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-496000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-649000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3132000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>377000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1618000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4700000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-310000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>549000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-572000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8625000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-925000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3423000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1503000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2342000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1177000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3427000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2333000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4046000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2133000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2586000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2839000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2917000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2583000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2462000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2145000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2103000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2203000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E24" s="3">
         <v>538000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-251000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-71000</v>
       </c>
-      <c r="G24" s="3">
-        <v>19000</v>
-      </c>
       <c r="H24" s="3">
+        <v>14000</v>
+      </c>
+      <c r="I24" s="3">
         <v>176000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>217000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-376000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-539000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-178000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-18000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-11000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-186000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-459000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1028000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-862000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1332000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-485000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>184000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>622000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-230000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>390000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>362000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>868000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>773000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>713000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>566000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>472000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2250,192 +2298,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1638000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-149000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-425000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-668000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-663000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-3308000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>160000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1242000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4161000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-132000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>567000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-561000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8439000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-466000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2395000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-641000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1010000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1167000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2942000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2149000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3424000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2363000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2196000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2477000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2049000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1810000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1749000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1579000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1631000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2279000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1636000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-149000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-414000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-639000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-634000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-3275000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>193000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1219000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4140000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-109000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>587000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-537000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8420000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-449000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2376000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-628000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1010000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1166000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2942000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2147000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3422000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2361000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2196000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2474000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2047000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1808000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1749000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1577000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1631000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2526,8 +2583,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2540,11 +2600,11 @@
       <c r="F29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" s="3">
         <v>5000</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>24</v>
@@ -2552,17 +2612,17 @@
       <c r="J29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="3">
         <v>-3000</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2582,8 +2642,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>24</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>24</v>
@@ -2600,11 +2660,11 @@
       <c r="Z29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB29" s="3">
         <v>1271000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>24</v>
@@ -2618,8 +2678,11 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2710,8 +2773,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2802,192 +2868,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-308000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-297000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-320000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-302000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-336000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-288000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-253000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-181000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-132000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-30000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-199000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-190000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-122000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-119000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-94000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-112000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-104000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-121000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-107000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-106000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-29000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>15000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-66000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-32000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1636000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-149000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-414000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-634000</v>
-      </c>
       <c r="H33" s="3">
+        <v>-629000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-3275000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>193000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1219000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4143000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-109000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>587000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-537000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8420000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-449000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2376000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-628000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1010000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1166000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2942000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2147000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3422000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2361000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2196000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2474000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3318000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1808000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1749000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1577000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3078,197 +3153,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1636000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-149000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-414000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-634000</v>
-      </c>
       <c r="H35" s="3">
+        <v>-629000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-3275000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>193000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1219000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4143000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-109000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>587000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-537000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8420000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-449000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2376000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-628000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1010000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1166000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2942000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2147000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3422000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2361000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2196000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2474000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3318000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1808000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1749000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1577000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3301,8 +3385,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3335,453 +3420,466 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12691000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6811000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7254000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10812000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14614000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13494000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10090000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7409000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8052000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9764000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8271000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7059000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7752000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10564000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19992000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>15039000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9485000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9763000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9167000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6836000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7637000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8034000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8121000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9235000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8813000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8569000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8737000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8190000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8801000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8986000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3274000</v>
+      </c>
+      <c r="E42" s="3">
         <v>6561000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6508000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3955000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2606000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>763000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1358000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4873000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8192000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10231000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13071000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>14861000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>17838000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>16552000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>12438000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>488000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>545000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1150000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>439000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>893000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>927000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1956000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1649000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>656000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1179000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1463000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1589000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1015000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1228000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>682000</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11065000</v>
+      </c>
+      <c r="E43" s="3">
         <v>12304000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12387000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12684000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11305000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12144000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12549000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11555000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11378000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12332000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11767000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11234000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10051000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11722000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11478000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12725000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12471000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>14808000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>13709000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>14217000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>14364000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>13260000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>12985000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>12868000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>11397000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>11079000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>10052000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>9915000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>9260000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>9889000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>79741000</v>
+      </c>
+      <c r="E44" s="3">
         <v>78972000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>78322000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>78503000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>78151000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>79777000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>79917000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>79819000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>78823000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>81897000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>81799000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>82668000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>81715000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>86961000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>83745000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>80020000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>76622000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>73279000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>68492000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>65369000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>62567000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>62038000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>61250000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>61303000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>33294000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>43031000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>42453000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>43247000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>43199000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>42680000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2504000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2287000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2941000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2857000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2847000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3073000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2086000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2356000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2221000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2664000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4187000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4123000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4286000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5213000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2624000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2739000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3106000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2656000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3304000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2194000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2335000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2398000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2396000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2481000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2417000</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AC45" s="3" t="s">
         <v>24</v>
@@ -3795,376 +3893,391 @@
       <c r="AF45" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>109275000</v>
+      </c>
+      <c r="E46" s="3">
         <v>106935000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>107412000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>108811000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>109523000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>109251000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>106000000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>106012000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>108666000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>116888000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>119095000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>119945000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>121642000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>131012000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>130277000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>111011000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>102229000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>101656000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>95111000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>89509000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>87830000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>87686000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>86401000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>86543000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>85194000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>64142000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>62831000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>62367000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>62488000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>62237000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1895000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2024000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2130000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2341000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2433000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2492000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2523000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2572000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2670000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2758000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2748000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2875000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2952000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3062000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3120000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3240000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3472000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3438000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3525000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3663000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3749000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4270000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4315000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4296000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4665000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5032000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5202000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5446000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5060000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10661000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10484000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10455000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10493000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10550000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10508000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10617000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10755000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10918000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11113000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11341000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11643000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13072000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11969000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12182000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12405000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13684000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13705000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13665000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13602000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12645000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12571000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12605000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12628000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12672000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12712000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12820000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12842000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12807000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12713000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10187000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10212000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10255000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10317000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10368000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10416000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10486000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10557000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10630000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9785000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9915000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9930000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10195000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10341000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10466000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11313000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11398000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11650000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>11812000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11465000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>11269000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8252000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8044000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8083000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8132000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7867000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7914000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7838000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7864000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7616000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4255,8 +4368,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4347,100 +4463,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4994000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4626000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4522000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4385000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4226000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4891000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5853000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5905000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5668000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6302000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5836000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5642000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4275000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4877000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6827000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5106000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2842000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2149000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2148000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1970000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1866000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1880000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1830000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1999000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1851000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1621000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1439000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1424000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1392000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4531,100 +4653,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>137012000</v>
+      </c>
+      <c r="E54" s="3">
         <v>134281000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>134774000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>136347000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>137100000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>137558000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>135479000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>135801000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>138552000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>146846000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>148935000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>150035000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>152136000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>161261000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>162872000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>143075000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>133625000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>132598000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>126261000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>120209000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>117359000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>114659000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>113195000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>113549000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>112362000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>91007000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>90036000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>89673000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>89997000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>88950000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4657,8 +4785,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4691,560 +4820,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11964000</v>
+      </c>
+      <c r="E57" s="3">
         <v>11143000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10936000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10274000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10200000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9793000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9575000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8779000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9261000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10151000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11450000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12410000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12928000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14479000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13700000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14963000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15553000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15101000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15267000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14693000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12916000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>13663000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12904000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12613000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12202000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12718000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12093000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11964000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11190000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11968000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5204000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4891000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4609000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7926000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5190000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5431000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5406000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2591000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1296000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5377000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6534000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6021000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1693000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3634000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2922000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5173000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>7340000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4354000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4357000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3381000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3190000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1389000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1611000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1981000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1335000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>988000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>720000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>367000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>384000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>632000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>78659000</v>
+      </c>
+      <c r="E59" s="3">
         <v>77028000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>76531000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>75310000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>74662000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>74394000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>69818000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>70322000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>71435000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>70243000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>70240000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>71461000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>72659000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>74194000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>75860000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>74366000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>74419000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>72391000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>72565000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>65541000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>65484000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>64365000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>63210000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>60938000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>101620000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>40703000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>40096000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>37450000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>38560000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>35889000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>95827000</v>
+      </c>
+      <c r="E60" s="3">
         <v>93062000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>92076000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>93510000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>90052000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>89618000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>84799000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>81692000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>81992000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>85771000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>88224000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>89892000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>87280000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>92307000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>92482000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>94502000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>97312000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>91846000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>92189000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>83615000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>81590000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>79417000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>77725000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>75532000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>74648000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>54409000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>52909000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>49781000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>50134000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>48489000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>47103000</v>
+      </c>
+      <c r="E61" s="3">
         <v>47381000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>47659000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>47465000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>51811000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>51788000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>51794000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>55150000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>56806000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>57042000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>57025000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>57554000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>61890000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>57325000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>58457000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>33754000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>19962000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>20298000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14859000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>11363000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10657000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10487000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10507000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10471000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9782000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9780000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10055000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10432000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9568000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9824000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11310000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10555000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10532000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10856000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11085000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13787000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13677000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14227000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14600000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18299000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20171000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20430000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>21041000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23182000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23315000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>24179000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>24651000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>24263000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>24156000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>24999000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>24702000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>25964000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>26337000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>26248000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>26219000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>25673000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>29050000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>29305000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>29418000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>28487000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5335,8 +5483,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5427,8 +5578,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5519,100 +5673,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>154245000</v>
+      </c>
+      <c r="E66" s="3">
         <v>151010000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>150291000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>151855000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>152983000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>155257000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>150367000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>151199000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>153551000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>161286000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>165617000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>168093000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>170452000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>173082000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>174539000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>152740000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>142242000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>136714000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>131583000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>120084000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>117020000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>115948000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>114636000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>112327000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>110706000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>89921000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>92073000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>89578000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>89180000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>86861000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5645,8 +5805,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5737,8 +5898,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5829,8 +5993,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5921,8 +6088,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6013,100 +6183,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>27251000</v>
+      </c>
+      <c r="E72" s="3">
         <v>27274000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>28910000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29059000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>29473000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>30107000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>33382000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>33189000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>34408000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>38551000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>38660000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>38073000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>38610000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>47029000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>47478000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>49854000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>50644000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>53986000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>52819000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>58090000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>55941000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>54666000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>52303000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>52095000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>49618000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>44052000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>42222000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>42165000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>40714000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>40641000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6197,8 +6373,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6289,8 +6468,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6381,100 +6563,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-17233000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-16729000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-15517000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-15508000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-15883000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-17699000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-14888000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-15398000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-14999000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-14440000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-16682000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-18058000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-18316000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-11821000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-11667000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-9665000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-8617000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-4116000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-5322000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>125000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>339000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-1289000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-1441000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1222000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1656000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1086000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-2037000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>95000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>817000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2089000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6565,197 +6753,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1636000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-149000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-414000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-634000</v>
-      </c>
       <c r="H81" s="3">
+        <v>-629000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-3275000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>193000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1219000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4143000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-109000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>587000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-537000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8420000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-449000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2376000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-628000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1010000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1166000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2942000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2147000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3422000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2361000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2196000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2474000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3318000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1808000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1749000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1577000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6788,100 +6985,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>481000</v>
+      </c>
+      <c r="E83" s="3">
         <v>467000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>456000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>457000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>502000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>493000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>498000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>486000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>534000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>523000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>551000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>536000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>578000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>565000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>547000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>556000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>628000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>576000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>546000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>521000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>583000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>523000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>507000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>501000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>582000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>522000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>494000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>471000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>546000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>474000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6972,8 +7173,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7064,8 +7268,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7156,8 +7363,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7248,8 +7458,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7340,100 +7553,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3381000</v>
+      </c>
+      <c r="E89" s="3">
         <v>22000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2875000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-318000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3457000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3190000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>81000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3216000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>716000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-262000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-483000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3387000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4009000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4819000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5280000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4302000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2220000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2424000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-590000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2788000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2947000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4559000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4680000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3136000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2903000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3396000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4949000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2098000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2832000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3202000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7466,100 +7685,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-431000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-332000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-296000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-468000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-326000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-284000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-263000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-349000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-222000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-245000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-222000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-291000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-265000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-262000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-348000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-428000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-447000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-465000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-421000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-501000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-495000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-457000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-376000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-394000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-435000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-399000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-439000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-932000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-599000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-595000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7650,8 +7873,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7742,100 +7968,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2804000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-403000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3015000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1823000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2151000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>290000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3266000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2965000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1935000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2966000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1659000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2764000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1543000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4137000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12307000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-379000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>517000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1194000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-86000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-767000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2424000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-902000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1414000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>119000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-457000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-218000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1123000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-260000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1416000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-614000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7868,8 +8100,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7916,52 +8149,55 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-1158000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1157000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-1156000</v>
       </c>
       <c r="U96" s="3">
         <v>-1156000</v>
       </c>
       <c r="V96" s="3">
+        <v>-1156000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-1161000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-970000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-979000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-991000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-842000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-855000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-852000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-868000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-672000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-676000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8052,8 +8288,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8144,8 +8383,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8236,280 +8478,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-356000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-38000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3413000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1680000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-250000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-18000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-602000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-396000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4362000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1171000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-19000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-48000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2681000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-468000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>22462000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>10280000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1403000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4240000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2919000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2823000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-856000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3689000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4332000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2845000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2241000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3335000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3311000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2463000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1574000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2204000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-24000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>10000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>61000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-63000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-68000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-20000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-18000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>59000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>37000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>36000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-47000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>22000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-25000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-16000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-44000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>8000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>7000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>21000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>32000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>20000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-27000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5881000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-443000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3811000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1117000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3399000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2677000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-650000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1716000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1513000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1161000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-689000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2812000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9387000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4911000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5552000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-278000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>597000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2240000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-801000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-349000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-33000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1110000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>418000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>212000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>547000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-605000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-185000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>381000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>BA</t>
   </si>
@@ -656,411 +656,423 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16569000</v>
+      </c>
+      <c r="E8" s="3">
         <v>22018000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>18104000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19751000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17921000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19980000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15956000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16681000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13991000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14793000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15278000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16998000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15217000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15802000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14139000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11807000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16908000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>20560000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>19980000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>21361000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>22917000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>28341000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>25146000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>24258000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>23382000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>24770000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>24223000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>23051000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>21961000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>23286000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>23898000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>14693000</v>
+      </c>
+      <c r="E9" s="3">
         <v>19321000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16939000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17812000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15998000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18124000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16778000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14559000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13645000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>17307000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13566000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14588000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13808000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>20992000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13105000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12978000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16768000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>18708000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>16930000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>17810000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>18645000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>22090000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>21040000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>19536000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>18824000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>19881000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>19956000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>18702000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>18073000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>19464000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>19904000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1876000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2697000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1165000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1939000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1923000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1856000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-822000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2122000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>346000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-2514000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1712000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2410000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1409000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-5190000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1034000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-1171000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>140000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1852000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3050000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3551000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4272000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>6251000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4106000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4722000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4558000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4889000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4267000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4349000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3888000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3822000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3994000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1094,103 +1106,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>868000</v>
+      </c>
+      <c r="E12" s="3">
         <v>881000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>958000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>797000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>741000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>794000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>727000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>698000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>633000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>678000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>575000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>497000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>499000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>605000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>574000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>625000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>672000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>749000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>778000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>826000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>866000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>852000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>826000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>827000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>764000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>762000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>768000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>813000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>836000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>726000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>857000</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1284,31 +1300,34 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>24</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>24</v>
@@ -1325,11 +1344,11 @@
       <c r="O14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="3">
         <v>498000</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>24</v>
@@ -1337,17 +1356,17 @@
       <c r="S14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U14" s="3">
         <v>2649000</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>5610000</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>24</v>
@@ -1358,8 +1377,8 @@
       <c r="Z14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1379,8 +1398,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1474,8 +1496,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1506,198 +1531,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>16655000</v>
+      </c>
+      <c r="E17" s="3">
         <v>21735000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18912000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>19850000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18070000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>20325000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18748000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15901000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15153000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18964000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14949000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15975000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15300000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23851000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14540000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14771000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18261000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>22764000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18721000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>24741000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>20567000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>24166000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>22919000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21548000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>20507000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>21792000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>21593000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>20521000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>19755000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>21103000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>21616000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="E18" s="3">
         <v>283000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-808000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-99000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-149000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-345000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2792000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>780000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1162000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4171000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>329000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1023000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-83000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8049000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-401000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2964000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1353000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2204000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1259000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3380000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2350000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4175000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2227000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2710000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2875000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2978000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2630000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2530000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2206000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2183000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2282000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1731,483 +1763,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>277000</v>
+      </c>
+      <c r="E20" s="3">
         <v>308000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>297000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>320000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>302000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>336000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>288000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>253000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>181000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>132000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>30000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>199000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>190000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>122000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>119000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>94000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>112000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>104000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>121000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>107000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>106000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>29000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>12000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>66000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>32000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>40000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>25000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>26000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>633000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1072000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-44000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>677000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>610000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>493000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2011000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1531000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-495000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3505000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>882000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1773000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>643000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7349000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>283000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2323000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-685000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1472000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1956000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2727000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2977000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4787000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2762000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3202000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3442000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3587000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3184000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3043000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2700000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2728000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2758000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>569000</v>
+      </c>
+      <c r="E22" s="3">
         <v>600000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>589000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>621000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>649000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>640000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>628000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>656000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>637000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>661000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>669000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>673000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>679000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>698000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>643000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>553000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>262000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>242000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>203000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>154000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>123000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>158000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>106000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>109000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>102000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>93000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>87000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>93000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>87000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>79000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-378000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1100000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-400000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-496000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-649000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3132000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>377000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1618000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4700000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-310000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>549000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-572000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8625000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-925000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3423000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1503000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2342000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1177000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3427000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2333000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4046000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2133000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2586000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2839000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2917000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2583000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2462000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2145000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2103000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2203000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E24" s="3">
         <v>21000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>538000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-251000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-71000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>176000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>217000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-376000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-539000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-178000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-18000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-11000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-186000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-459000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1028000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-862000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1332000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>10000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-485000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>184000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>622000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-230000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>390000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>362000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>868000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>773000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>713000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>566000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>472000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2301,198 +2349,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-355000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-30000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1638000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-149000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-425000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-663000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3308000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>160000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1242000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4161000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-132000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>567000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-561000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8439000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-466000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2395000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-641000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1010000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1167000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2942000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2149000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3424000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2363000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2196000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2477000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2049000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1810000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1749000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1579000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1631000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2279000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-343000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1636000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-149000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-414000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-634000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3275000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>193000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1219000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4140000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-109000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>587000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-537000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8420000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-449000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2376000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-628000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1010000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1166000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2942000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2147000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3422000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2361000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2196000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2474000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2047000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1808000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1749000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1577000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1631000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2586,8 +2643,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,11 +2663,11 @@
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="3">
         <v>5000</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>24</v>
@@ -2615,17 +2675,17 @@
       <c r="K29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="3">
         <v>-3000</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2645,8 +2705,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>24</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>24</v>
@@ -2663,11 +2723,11 @@
       <c r="AA29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC29" s="3">
         <v>1271000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>24</v>
@@ -2681,8 +2741,11 @@
       <c r="AG29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2776,8 +2839,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2871,198 +2937,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-277000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-308000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-297000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-320000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-302000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-336000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-288000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-253000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-181000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-132000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-30000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-199000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-190000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-122000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-119000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-94000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-112000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-104000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-121000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-107000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-106000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>15000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-66000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-32000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-343000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1636000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-149000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-414000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-629000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3275000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>193000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1219000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4143000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-109000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>587000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-537000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8420000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-449000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2376000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-628000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1010000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1166000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2942000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2147000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3422000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2361000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2196000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2474000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3318000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1808000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1749000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1577000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3156,203 +3231,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-343000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1636000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-149000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-414000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-629000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3275000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>193000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1219000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4143000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-109000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>587000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-537000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8420000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-449000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2376000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-628000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1010000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1166000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2942000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2147000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3422000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2361000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2196000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2474000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3318000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1808000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1749000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1577000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3386,8 +3470,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3421,468 +3506,481 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6914000</v>
+      </c>
+      <c r="E41" s="3">
         <v>12691000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6811000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7254000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10812000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14614000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13494000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10090000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7409000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8052000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9764000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8271000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7059000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7752000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10564000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>19992000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>15039000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9485000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9763000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9167000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6836000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7637000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8034000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8121000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9235000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8813000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8569000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8737000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8190000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8801000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8986000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>615000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3274000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6561000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6508000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3955000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2606000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>763000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1358000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4873000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8192000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10231000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13071000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>14861000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>17838000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>16552000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>12438000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>488000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>545000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1150000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>439000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>893000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>927000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1956000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1649000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>656000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1179000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1463000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1589000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1015000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1228000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>682000</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12689000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11065000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12304000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12387000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12684000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11305000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12144000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12549000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11555000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11378000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12332000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11767000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11234000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10051000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11722000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11478000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12725000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12471000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>14808000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>13709000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>14217000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>14364000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>13260000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>12985000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>12868000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>11397000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>11079000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>10052000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>9915000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>9260000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>9889000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>83471000</v>
+      </c>
+      <c r="E44" s="3">
         <v>79741000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>78972000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>78322000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>78503000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>78151000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>79777000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>79917000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>79819000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>78823000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>81897000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>81799000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>82668000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>81715000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>86961000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>83745000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>80020000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>76622000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>73279000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>68492000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>65369000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>62567000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>62038000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>61250000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>61303000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>33294000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>43031000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>42453000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>43247000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>43199000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>42680000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2843000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2504000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2287000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2941000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2857000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2847000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3073000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2086000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2356000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2221000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2664000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4187000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4123000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4286000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5213000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2624000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2739000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3106000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2656000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3304000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2194000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2335000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2398000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2396000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2481000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2417000</v>
-      </c>
-      <c r="AC45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AD45" s="3" t="s">
         <v>24</v>
@@ -3896,388 +3994,403 @@
       <c r="AG45" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>106532000</v>
+      </c>
+      <c r="E46" s="3">
         <v>109275000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>106935000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>107412000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>108811000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>109523000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>109251000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>106000000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>106012000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>108666000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>116888000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>119095000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>119945000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>121642000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>131012000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>130277000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>111011000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>102229000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>101656000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>95111000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>89509000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>87830000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>87686000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>86401000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>86543000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>85194000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>64142000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>62831000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>62367000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>62488000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>62237000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1875000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1895000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2024000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2130000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2341000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2433000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2492000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2523000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2572000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2670000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2758000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2748000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2875000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2952000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3062000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3120000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3240000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3472000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3438000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3525000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3663000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3749000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4270000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4315000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4296000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4665000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5032000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5202000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5446000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5060000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10696000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10661000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10484000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10455000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10493000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10550000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10508000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10617000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10755000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10918000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11113000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11341000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11643000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13072000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11969000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12182000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12405000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13684000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13705000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13665000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13602000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12645000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12571000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12605000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12628000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12672000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12712000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12820000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12842000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12807000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12713000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10123000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10187000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10212000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10255000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10317000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10368000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10416000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10486000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10557000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10630000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9785000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9915000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9930000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10195000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10341000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10466000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11313000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11398000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>11650000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11812000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>11465000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>11269000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8252000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8044000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8083000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8132000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7867000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7914000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7838000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7864000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>7616000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4371,8 +4484,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4466,103 +4582,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5258000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4994000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4626000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4522000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4385000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4226000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4891000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5853000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5905000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5668000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6302000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5836000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5642000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4275000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4877000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6827000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5106000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2842000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2149000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2148000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1970000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1866000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1880000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1830000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1999000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1851000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1621000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1439000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1424000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1392000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4656,103 +4778,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>134484000</v>
+      </c>
+      <c r="E54" s="3">
         <v>137012000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>134281000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>134774000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>136347000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>137100000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>137558000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>135479000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>135801000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>138552000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>146846000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>148935000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>150035000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>152136000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>161261000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>162872000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>143075000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>133625000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>132598000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>126261000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>120209000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>117359000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>114659000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>113195000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>113549000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>112362000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>91007000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>90036000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>89673000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>89997000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>88950000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4786,8 +4914,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4821,578 +4950,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11616000</v>
+      </c>
+      <c r="E57" s="3">
         <v>11964000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11143000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10936000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10274000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10200000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9793000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9575000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8779000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9261000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10151000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11450000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12410000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12928000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14479000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13700000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14963000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15553000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15101000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15267000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>14693000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12916000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>13663000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12904000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12613000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12202000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12718000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12093000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11964000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11190000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11968000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1063000</v>
+      </c>
+      <c r="E58" s="3">
         <v>5204000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4891000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4609000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7926000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5190000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5431000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5406000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2591000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1296000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5377000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6534000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6021000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1693000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3634000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2922000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5173000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>7340000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4354000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4357000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3381000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3190000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1389000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1611000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1981000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1335000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>988000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>720000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>367000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>384000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>632000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>80579000</v>
+      </c>
+      <c r="E59" s="3">
         <v>78659000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>77028000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>76531000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>75310000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>74662000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>74394000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>69818000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>70322000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>71435000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>70243000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>70240000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>71461000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>72659000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>74194000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>75860000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>74366000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>74419000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>72391000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>72565000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>65541000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>65484000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>64365000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>63210000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>60938000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>101620000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>40703000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>40096000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>37450000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>38560000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>35889000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>93258000</v>
+      </c>
+      <c r="E60" s="3">
         <v>95827000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>93062000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>92076000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>93510000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>90052000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>89618000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>84799000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>81692000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>81992000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>85771000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>88224000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>89892000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>87280000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>92307000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>92482000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>94502000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>97312000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>91846000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>92189000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>83615000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>81590000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>79417000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>77725000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>75532000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>74648000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>54409000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>52909000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>49781000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>50134000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>48489000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>46877000</v>
+      </c>
+      <c r="E61" s="3">
         <v>47103000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>47381000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>47659000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>47465000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>51811000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>51788000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>51794000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>55150000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>56806000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>57042000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>57025000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>57554000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>61890000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>57325000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>58457000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>33754000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>19962000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>20298000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14859000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>11363000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10657000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10487000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10507000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10471000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9782000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9780000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10055000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10432000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9568000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9824000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11365000</v>
+      </c>
+      <c r="E62" s="3">
         <v>11310000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10555000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10532000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10856000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11085000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13787000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13677000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14227000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14600000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18299000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20171000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20430000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>21041000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23182000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23315000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>24179000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>24651000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>24263000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>24156000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>24999000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>24702000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>25964000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>26337000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>26248000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>26219000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>25673000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>29050000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>29305000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>29418000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>28487000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5486,8 +5634,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5581,8 +5732,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5676,103 +5830,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>151493000</v>
+      </c>
+      <c r="E66" s="3">
         <v>154245000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>151010000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>150291000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>151855000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>152983000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>155257000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>150367000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>151199000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>153551000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>161286000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>165617000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>168093000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>170452000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>173082000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>174539000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>152740000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>142242000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>136714000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>131583000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>120084000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>117020000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>115948000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>114636000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>112327000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>110706000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>89921000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>92073000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>89578000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>89180000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>86861000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5806,8 +5966,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5901,8 +6062,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5996,8 +6160,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6091,8 +6258,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6186,103 +6356,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>26908000</v>
+      </c>
+      <c r="E72" s="3">
         <v>27251000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>27274000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>28910000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>29059000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>29473000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>30107000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>33382000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>33189000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>34408000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>38551000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>38660000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>38073000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>38610000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>47029000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>47478000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>49854000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>50644000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>53986000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>52819000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>58090000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>55941000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>54666000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>52303000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>52095000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>49618000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>44052000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>42222000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>42165000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>40714000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>40641000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6376,8 +6552,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6471,8 +6650,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6566,103 +6748,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-17009000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-17233000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-16729000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-15517000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-15508000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-15883000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-17699000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-14888000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-15398000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-14999000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-14440000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-16682000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-18058000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-18316000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-11821000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-11667000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-9665000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-8617000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-4116000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-5322000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>125000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>339000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-1289000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-1441000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1222000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1656000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1086000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-2037000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>95000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>817000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2089000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6756,203 +6944,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-343000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1636000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-149000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-414000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-629000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3275000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>193000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1219000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4143000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-109000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>587000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-537000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8420000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-449000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2376000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-628000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1010000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1166000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2942000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2147000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3422000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2361000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2196000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2474000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3318000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1808000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1749000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1577000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6986,103 +7183,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>442000</v>
+      </c>
+      <c r="E83" s="3">
         <v>481000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>467000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>456000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>457000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>502000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>493000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>498000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>486000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>534000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>523000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>551000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>536000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>578000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>565000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>547000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>556000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>628000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>576000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>546000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>521000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>583000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>523000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>507000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>501000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>582000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>522000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>494000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>471000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>546000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>474000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7176,8 +7377,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7271,8 +7475,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7366,8 +7573,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7461,8 +7671,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7556,103 +7769,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3362000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3381000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>22000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2875000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-318000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3457000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3190000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>81000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3216000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>716000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-262000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-483000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3387000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4009000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4819000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5280000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4302000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2220000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2424000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-590000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2788000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2947000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4559000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4680000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3136000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2903000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3396000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4949000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2098000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2832000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3202000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7686,103 +7905,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-567000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-431000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-332000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-296000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-468000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-326000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-284000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-263000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-349000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-222000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-245000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-222000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-291000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-265000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-262000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-348000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-428000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-447000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-465000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-421000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-501000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-495000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-457000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-376000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-394000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-435000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-399000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-439000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-932000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-599000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-595000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7876,8 +8099,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7971,103 +8197,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2074000</v>
+      </c>
+      <c r="E94" s="3">
         <v>2804000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-403000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3015000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1823000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2151000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>290000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3266000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2965000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1935000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2966000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1659000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2764000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1543000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4137000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12307000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-379000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>517000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1194000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-86000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-767000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2424000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-902000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1414000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>119000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-457000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-218000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1123000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-260000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1416000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-614000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8101,8 +8333,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8152,52 +8385,55 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-1158000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1157000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-1156000</v>
       </c>
       <c r="V96" s="3">
         <v>-1156000</v>
       </c>
       <c r="W96" s="3">
+        <v>-1156000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-1161000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-970000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-979000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-991000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-842000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-855000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-852000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-868000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-672000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-676000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8291,8 +8527,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8386,8 +8625,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8481,289 +8723,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4462000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-356000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-38000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3413000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1680000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-250000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-18000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-602000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-396000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4362000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1171000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-19000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-48000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2681000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-468000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>22462000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>10280000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1403000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4240000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2919000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2823000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-856000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3689000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4332000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2845000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2241000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3335000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3311000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2463000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1574000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2204000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E101" s="3">
         <v>52000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-24000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>10000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>61000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-63000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-68000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-20000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-18000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>59000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>37000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>36000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-47000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>22000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-25000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-44000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>8000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>7000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>21000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>32000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>20000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-27000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5778000</v>
+      </c>
+      <c r="E102" s="3">
         <v>5881000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-443000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3811000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1117000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3399000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2677000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-650000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1716000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1513000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1161000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-689000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2812000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9387000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4911000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5552000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-278000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>597000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2240000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-801000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-349000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-33000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1110000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>418000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>212000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>547000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-605000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-185000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>381000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>BA</t>
   </si>
@@ -656,423 +656,435 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16866000</v>
+      </c>
+      <c r="E8" s="3">
         <v>16569000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22018000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>18104000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19751000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>17921000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19980000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15956000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16681000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13991000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14793000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15278000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16998000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15217000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15802000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14139000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11807000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16908000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>20560000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>19980000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>21361000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>22917000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>28341000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>25146000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>24258000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>23382000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>24770000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>24223000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>23051000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>21961000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>23286000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>23898000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>15637000</v>
+      </c>
+      <c r="E9" s="3">
         <v>14693000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19321000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16939000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17812000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15998000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18124000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16778000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14559000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13645000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>17307000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13566000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14588000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13808000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>20992000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13105000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12978000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16768000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>18708000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>16930000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>17810000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>18645000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>22090000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>21040000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>19536000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>18824000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>19881000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>19956000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>18702000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>18073000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>19464000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>19904000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1229000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1876000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2697000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1165000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1939000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1923000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1856000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-822000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2122000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>346000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-2514000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1712000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2410000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1409000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-5190000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1034000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-1171000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>140000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1852000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3050000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3551000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4272000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6251000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4106000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4722000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4558000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4889000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4267000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4349000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3888000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3822000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3994000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1107,106 +1119,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>954000</v>
+      </c>
+      <c r="E12" s="3">
         <v>868000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>881000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>958000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>797000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>741000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>794000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>727000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>698000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>633000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>678000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>575000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>497000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>499000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>605000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>574000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>625000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>672000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>749000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>778000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>826000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>866000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>852000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>826000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>827000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>764000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>762000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>768000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>813000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>836000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>726000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>857000</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1303,8 +1319,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1329,8 +1348,8 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>24</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>24</v>
@@ -1347,11 +1366,11 @@
       <c r="P14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R14" s="3">
         <v>498000</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>24</v>
@@ -1359,17 +1378,17 @@
       <c r="T14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V14" s="3">
         <v>2649000</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>5610000</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>24</v>
@@ -1380,8 +1399,8 @@
       <c r="AA14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1401,8 +1420,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1499,8 +1521,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1532,204 +1557,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>17956000</v>
+      </c>
+      <c r="E17" s="3">
         <v>16655000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21735000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18912000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19850000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18070000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20325000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18748000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15901000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15153000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18964000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14949000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15975000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15300000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23851000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14540000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14771000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18261000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22764000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18721000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>24741000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>20567000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>24166000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>22919000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>21548000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>20507000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>21792000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>21593000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>20521000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>19755000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>21103000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>21616000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-1090000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-86000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>283000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-808000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-99000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-149000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-345000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2792000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>780000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1162000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4171000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>329000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1023000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-83000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8049000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-401000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2964000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1353000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2204000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1259000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3380000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2350000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4175000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2227000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2710000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2875000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2978000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2630000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2530000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2206000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2183000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2282000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1764,498 +1796,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>248000</v>
+      </c>
+      <c r="E20" s="3">
         <v>277000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>308000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>297000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>320000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>302000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>336000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>288000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>253000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>181000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>132000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>30000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>199000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>190000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>122000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>119000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>94000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>112000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>104000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>121000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>107000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>106000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>29000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>12000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>66000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>32000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>40000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>25000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>26000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-401000</v>
+      </c>
+      <c r="E21" s="3">
         <v>633000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1072000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-44000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>677000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>610000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>493000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2011000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1531000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-495000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3505000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>882000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1773000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>643000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7349000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>283000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2323000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-685000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1472000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1956000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2727000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2977000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4787000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2762000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3202000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3442000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3587000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3184000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3043000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2700000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2728000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2758000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>673000</v>
+      </c>
+      <c r="E22" s="3">
         <v>569000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>600000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>589000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>621000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>649000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>640000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>628000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>656000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>637000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>661000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>669000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>673000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>679000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>698000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>643000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>553000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>262000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>242000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>203000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>154000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>123000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>158000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>106000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>109000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>102000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>93000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>87000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>93000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>87000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>79000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-1515000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-378000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1100000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-400000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-496000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-649000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3132000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>377000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1618000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4700000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-310000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>549000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-572000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8625000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-925000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3423000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1503000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2342000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1177000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3427000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2333000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4046000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2133000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2586000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2839000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2917000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2583000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2462000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2145000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2103000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2203000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-23000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>21000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>538000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-251000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-71000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>176000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>217000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-376000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-539000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-178000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-18000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-186000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-459000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1028000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-862000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1332000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>10000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-485000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>184000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>622000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-230000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>390000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>362000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>868000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>773000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>713000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>566000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>472000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2352,204 +2400,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-1439000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-355000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-30000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1638000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-149000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-425000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-663000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3308000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>160000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1242000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4161000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-132000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>567000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-561000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8439000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-466000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2395000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-641000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1010000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1167000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2942000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2149000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3424000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2363000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2196000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2477000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2049000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1810000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1749000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1579000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1631000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2279000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-1439000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-343000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1636000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-149000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-414000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-634000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3275000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>193000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1219000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4140000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-109000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>587000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-537000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8420000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-449000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2376000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-628000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1010000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1166000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2942000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2147000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3422000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2361000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2196000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2474000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2047000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1808000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1749000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1577000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1631000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2646,8 +2703,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2666,11 +2726,11 @@
       <c r="H29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="3">
         <v>5000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>24</v>
@@ -2678,17 +2738,17 @@
       <c r="L29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N29" s="3">
         <v>-3000</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2708,8 +2768,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>24</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>24</v>
@@ -2726,11 +2786,11 @@
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD29" s="3">
         <v>1271000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -2744,8 +2804,11 @@
       <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2842,8 +2905,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2940,204 +3006,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-277000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-308000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-297000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-320000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-302000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-336000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-288000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-253000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-181000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-132000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-30000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-199000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-190000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-122000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-119000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-94000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-112000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-104000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-121000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-107000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-106000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>15000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-66000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-32000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1439000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-343000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1636000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-149000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-414000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-629000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3275000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>193000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1219000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4143000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-109000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>587000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-537000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8420000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-449000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2376000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-628000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1010000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1166000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2942000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2147000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3422000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2361000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2196000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2474000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3318000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1808000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1749000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1577000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3234,209 +3309,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1439000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-343000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1636000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-149000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-414000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-629000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3275000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>193000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1219000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4143000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-109000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>587000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-537000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8420000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-449000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2376000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-628000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1010000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1166000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2942000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2147000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3422000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2361000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2196000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2474000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3318000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1808000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1749000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1577000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3471,8 +3555,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3507,483 +3592,496 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10894000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6914000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12691000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6811000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7254000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10812000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14614000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13494000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10090000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7409000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8052000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9764000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8271000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7059000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7752000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10564000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>19992000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>15039000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9485000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9763000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9167000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6836000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7637000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8034000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8121000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9235000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8813000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8569000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8737000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8190000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8801000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8986000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1727000</v>
+      </c>
+      <c r="E42" s="3">
         <v>615000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3274000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6561000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6508000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3955000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2606000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>763000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1358000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4873000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8192000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>10231000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>13071000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>14861000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>17838000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>16552000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>12438000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>488000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>545000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1150000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>439000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>893000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>927000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1956000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1649000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>656000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1179000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1463000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1589000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1015000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1228000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>682000</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12875000</v>
+      </c>
+      <c r="E43" s="3">
         <v>12689000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11065000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12304000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12387000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12684000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11305000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12144000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12549000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11555000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11378000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12332000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11767000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11234000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10051000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11722000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11478000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12725000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12471000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>14808000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>13709000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>14217000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>14364000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>13260000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>12985000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>12868000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>11397000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>11079000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>10052000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>9915000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>9260000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>9889000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>85661000</v>
+      </c>
+      <c r="E44" s="3">
         <v>83471000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>79741000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>78972000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>78322000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>78503000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>78151000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>79777000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>79917000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>79819000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>78823000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>81897000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>81799000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>82668000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>81715000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>86961000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>83745000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>80020000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>76622000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>73279000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>68492000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>65369000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>62567000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>62038000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>61250000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>61303000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>33294000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>43031000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>42453000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>43247000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>43199000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>42680000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3282000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2843000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2504000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2287000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2941000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2857000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2847000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3073000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2086000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2356000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2221000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2664000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4187000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4123000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4286000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5213000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2624000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2739000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3106000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2656000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3304000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2194000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2335000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2398000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2396000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2481000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2417000</v>
-      </c>
-      <c r="AD45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE45" s="3" t="s">
         <v>24</v>
@@ -3997,400 +4095,415 @@
       <c r="AH45" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>114439000</v>
+      </c>
+      <c r="E46" s="3">
         <v>106532000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>109275000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>106935000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>107412000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>108811000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>109523000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>109251000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>106000000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>106012000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>108666000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>116888000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>119095000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>119945000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>121642000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>131012000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>130277000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>111011000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>102229000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>101656000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>95111000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>89509000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>87830000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>87686000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>86401000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>86543000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>85194000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>64142000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>62831000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>62367000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>62488000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>62237000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1875000</v>
+        <v>1500000</v>
       </c>
       <c r="E47" s="3">
+        <v>1532000</v>
+      </c>
+      <c r="F47" s="3">
         <v>1895000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2024000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2130000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2341000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2433000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2492000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2523000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2572000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2670000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2758000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2748000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2875000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2952000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3062000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3120000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3240000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3472000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3438000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3525000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3663000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3749000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4270000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4315000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4296000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4665000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5032000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5202000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5446000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5060000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>10696000</v>
+        <v>11287000</v>
       </c>
       <c r="E48" s="3">
+        <v>11039000</v>
+      </c>
+      <c r="F48" s="3">
         <v>10661000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10484000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10455000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10493000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10550000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10508000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10617000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10755000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10918000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11113000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11341000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11643000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13072000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11969000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12182000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12405000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13684000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13705000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13665000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13602000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12645000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12571000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12605000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12628000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12672000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12712000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12820000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12842000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12807000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12713000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10175000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10123000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10187000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10212000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10255000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10317000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10368000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10416000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10486000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10557000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10630000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9785000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9915000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9930000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10195000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10341000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10466000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11313000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>11398000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11650000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>11812000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>11465000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11269000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8252000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8044000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8083000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8132000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7867000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7914000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7838000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>7864000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>7616000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4487,8 +4600,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4585,106 +4701,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5319000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5258000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4994000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4626000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4522000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4385000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4226000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4891000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5853000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5905000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5668000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6302000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5836000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5642000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4275000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4877000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6827000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5106000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2842000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2149000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2148000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1970000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1866000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1880000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1830000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1999000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1851000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1621000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1439000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1424000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1392000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4781,106 +4903,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>142720000</v>
+      </c>
+      <c r="E54" s="3">
         <v>134484000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>137012000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>134281000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>134774000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>136347000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>137100000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>137558000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>135479000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>135801000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>138552000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>146846000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>148935000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>150035000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>152136000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>161261000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>162872000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>143075000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>133625000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>132598000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>126261000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>120209000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>117359000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>114659000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>113195000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>113549000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>112362000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>91007000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>90036000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>89673000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>89997000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>88950000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4915,8 +5043,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4951,596 +5080,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11864000</v>
+      </c>
+      <c r="E57" s="3">
         <v>11616000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11964000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11143000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10936000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10274000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10200000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9793000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9575000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8779000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9261000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10151000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11450000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12410000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12928000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14479000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13700000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14963000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15553000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15101000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>15267000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>14693000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12916000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13663000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12904000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12613000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12202000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12718000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12093000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11964000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11190000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11968000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4765000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1063000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5204000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4891000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4609000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7926000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5190000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5431000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5406000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2591000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1296000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5377000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6534000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6021000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1693000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3634000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2922000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5173000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>7340000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4354000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4357000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3381000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3190000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1389000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1611000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1981000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1335000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>988000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>720000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>367000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>384000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>632000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>80001000</v>
+      </c>
+      <c r="E59" s="3">
         <v>80579000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>78659000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>77028000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>76531000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>75310000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>74662000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>74394000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>69818000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>70322000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>71435000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>70243000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>70240000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>71461000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>72659000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>74194000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>75860000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>74366000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>74419000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>72391000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>72565000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>65541000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>65484000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>64365000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>63210000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>60938000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>101620000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>40703000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>40096000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>37450000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>38560000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>35889000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>96630000</v>
+      </c>
+      <c r="E60" s="3">
         <v>93258000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>95827000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>93062000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>92076000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>93510000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>90052000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>89618000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>84799000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>81692000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>81992000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>85771000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>88224000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>89892000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>87280000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>92307000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>92482000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>94502000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>97312000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>91846000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>92189000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>83615000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>81590000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>79417000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>77725000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>75532000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>74648000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>54409000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>52909000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>49781000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>50134000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>48489000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>53162000</v>
+      </c>
+      <c r="E61" s="3">
         <v>46877000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>47103000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>47381000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>47659000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>47465000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>51811000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>51788000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51794000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>55150000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>56806000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>57042000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>57025000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>57554000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>61890000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>57325000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>58457000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>33754000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>19962000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>20298000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>14859000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>11363000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10657000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10487000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10507000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10471000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9782000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9780000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10055000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10432000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9568000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9824000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10910000</v>
+      </c>
+      <c r="E62" s="3">
         <v>11365000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11310000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10555000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10532000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10856000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11085000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13787000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13677000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14227000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14600000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18299000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20171000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>20430000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>21041000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23182000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>23315000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>24179000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>24651000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>24263000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>24156000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>24999000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>24702000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>25964000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>26337000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>26248000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>26219000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>25673000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>29050000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>29305000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>29418000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>28487000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5637,8 +5785,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5735,8 +5886,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5833,106 +5987,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>160696000</v>
+      </c>
+      <c r="E66" s="3">
         <v>151493000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>154245000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>151010000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>150291000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>151855000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>152983000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>155257000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>150367000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>151199000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>153551000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>161286000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>165617000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>168093000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>170452000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>173082000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>174539000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>152740000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>142242000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>136714000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>131583000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>120084000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>117020000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>115948000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>114636000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>112327000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>110706000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>89921000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>92073000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>89578000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>89180000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>86861000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5967,8 +6127,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6065,8 +6226,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6163,8 +6327,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6261,8 +6428,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6359,106 +6529,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>25469000</v>
+      </c>
+      <c r="E72" s="3">
         <v>26908000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>27251000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>27274000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>28910000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>29059000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>29473000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>30107000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>33382000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>33189000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>34408000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>38551000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>38660000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>38073000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>38610000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>47029000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>47478000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>49854000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>50644000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>53986000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>52819000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>58090000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>55941000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>54666000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>52303000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>52095000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>49618000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>44052000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>42222000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>42165000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>40714000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>40641000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6555,8 +6731,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6653,8 +6832,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6751,106 +6933,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-17976000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-17009000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-17233000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-16729000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-15517000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-15508000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-15883000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-17699000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-14888000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-15398000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-14999000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-14440000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-16682000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-18058000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-18316000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-11821000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-11667000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-9665000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-8617000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-4116000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-5322000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>125000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>339000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-1289000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-1441000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1222000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1656000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1086000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-2037000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>95000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>817000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2089000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6947,209 +7135,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1439000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-343000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1636000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-149000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-414000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-629000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3275000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>193000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1219000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4143000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-109000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>587000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-537000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8420000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-449000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2376000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-628000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1010000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1166000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2942000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2147000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3422000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2361000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2196000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2474000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3318000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1808000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1749000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1577000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7184,106 +7381,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>441000</v>
+      </c>
+      <c r="E83" s="3">
         <v>442000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>481000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>467000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>456000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>457000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>502000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>493000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>498000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>486000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>534000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>523000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>551000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>536000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>578000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>565000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>547000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>556000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>628000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>576000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>546000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>521000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>583000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>523000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>507000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>501000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>582000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>522000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>494000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>471000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>546000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>474000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7380,8 +7581,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7478,8 +7682,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7576,8 +7783,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7674,8 +7884,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7772,106 +7985,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3923000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3362000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3381000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>22000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2875000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-318000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3457000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3190000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>81000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3216000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>716000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-262000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-483000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3387000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4009000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4819000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5280000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4302000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2220000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2424000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-590000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2788000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2947000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4559000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4680000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3136000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2903000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3396000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4949000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2098000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2832000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3202000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7906,106 +8125,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-492000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-567000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-431000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-332000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-296000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-468000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-326000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-284000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-263000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-349000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-222000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-245000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-222000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-291000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-265000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-262000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-348000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-428000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-447000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-465000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-421000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-501000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-495000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-457000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-376000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-394000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-435000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-399000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-439000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-932000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-599000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-595000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8102,8 +8325,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8200,106 +8426,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2100000</v>
+      </c>
+      <c r="E94" s="3">
         <v>2074000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2804000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-403000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3015000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1823000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2151000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>290000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3266000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2965000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1935000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2966000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1659000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2764000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1543000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4137000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12307000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-379000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>517000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1194000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-86000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-767000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2424000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-902000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1414000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>119000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-457000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-218000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1123000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-260000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1416000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-614000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8334,8 +8566,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8388,52 +8621,55 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-1158000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1157000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-1156000</v>
       </c>
       <c r="W96" s="3">
         <v>-1156000</v>
       </c>
       <c r="X96" s="3">
+        <v>-1156000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-1161000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-970000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-979000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-991000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-842000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-855000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-852000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-868000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-672000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-676000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8530,8 +8766,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8628,8 +8867,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8726,298 +8968,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10000000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4462000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-356000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-38000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3413000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1680000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-250000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-602000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-396000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4362000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1171000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-19000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-48000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2681000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-468000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>22462000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>10280000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1403000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4240000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2919000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2823000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-856000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3689000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4332000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2845000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2241000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3335000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3311000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2463000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1574000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2204000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-28000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>52000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-24000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>10000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>61000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-63000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-68000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-20000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>59000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>37000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>36000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-47000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>22000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-25000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-44000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>8000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>7000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>21000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>32000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>20000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-27000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3980000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5778000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5881000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-443000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3811000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1117000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3399000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2677000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-650000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1716000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1513000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1161000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-689000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2812000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9387000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4911000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5552000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-278000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>597000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2240000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-801000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-349000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-33000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1110000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>418000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>212000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>547000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-605000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-185000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>381000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>BA</t>
   </si>
@@ -656,435 +656,447 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>17840000</v>
+      </c>
+      <c r="E8" s="3">
         <v>16866000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16569000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22018000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>18104000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19751000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>17921000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19980000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15956000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16681000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13991000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14793000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15278000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16998000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15217000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15802000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14139000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11807000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16908000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>20560000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>19980000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>21361000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>22917000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>28341000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>25146000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>24258000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>23382000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>24770000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>24223000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>23051000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>21961000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>23286000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>23898000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>21347000</v>
+      </c>
+      <c r="E9" s="3">
         <v>15637000</v>
       </c>
-      <c r="E9" s="3">
-        <v>14693000</v>
-      </c>
       <c r="F9" s="3">
-        <v>19321000</v>
+        <v>14613000</v>
       </c>
       <c r="G9" s="3">
+        <v>19173000</v>
+      </c>
+      <c r="H9" s="3">
         <v>16939000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17812000</v>
       </c>
-      <c r="I9" s="3">
-        <v>15998000</v>
-      </c>
       <c r="J9" s="3">
+        <v>15493000</v>
+      </c>
+      <c r="K9" s="3">
         <v>18124000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16778000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14559000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13645000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17307000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13566000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14588000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13808000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>20992000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13105000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12978000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>16768000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>18708000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>16930000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>17810000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>18645000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>22090000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>21040000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>19536000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>18824000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>19881000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>19956000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>18702000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>18073000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>19464000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>19904000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-3507000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1229000</v>
       </c>
-      <c r="E10" s="3">
-        <v>1876000</v>
-      </c>
       <c r="F10" s="3">
-        <v>2697000</v>
+        <v>1956000</v>
       </c>
       <c r="G10" s="3">
+        <v>2845000</v>
+      </c>
+      <c r="H10" s="3">
         <v>1165000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1939000</v>
       </c>
-      <c r="I10" s="3">
-        <v>1923000</v>
-      </c>
       <c r="J10" s="3">
+        <v>2428000</v>
+      </c>
+      <c r="K10" s="3">
         <v>1856000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-822000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2122000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>346000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-2514000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1712000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2410000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1409000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-5190000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1034000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-1171000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>140000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1852000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3050000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3551000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4272000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6251000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4106000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4722000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4558000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4889000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4267000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4349000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3888000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3822000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3994000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1120,109 +1132,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1154000</v>
+      </c>
+      <c r="E12" s="3">
         <v>954000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>868000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>881000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>958000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>797000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>741000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>794000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>727000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>698000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>633000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>678000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>575000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>497000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>499000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>605000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>574000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>625000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>672000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>749000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>778000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>826000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>866000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>852000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>826000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>827000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>764000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>762000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>768000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>813000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>836000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>726000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>857000</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1322,37 +1338,40 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+        <v>147000</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>532000</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>24</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>24</v>
@@ -1369,11 +1388,11 @@
       <c r="Q14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S14" s="3">
         <v>498000</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>24</v>
@@ -1381,17 +1400,17 @@
       <c r="U14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="W14" s="3">
         <v>2649000</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="X14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5610000</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>24</v>
@@ -1402,8 +1421,8 @@
       <c r="AB14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1423,31 +1442,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>444000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>441000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>442000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>481000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>467000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>456000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>457000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1524,8 +1546,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1558,210 +1583,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>17956000</v>
+        <v>23445000</v>
       </c>
       <c r="E17" s="3">
-        <v>16655000</v>
+        <v>17827000</v>
       </c>
       <c r="F17" s="3">
-        <v>21735000</v>
+        <v>16501000</v>
       </c>
       <c r="G17" s="3">
-        <v>18912000</v>
+        <v>21448000</v>
       </c>
       <c r="H17" s="3">
-        <v>19850000</v>
+        <v>18791000</v>
       </c>
       <c r="I17" s="3">
-        <v>18070000</v>
+        <v>19747000</v>
       </c>
       <c r="J17" s="3">
+        <v>17389000</v>
+      </c>
+      <c r="K17" s="3">
         <v>20325000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18748000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15901000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15153000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18964000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14949000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15975000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15300000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23851000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14540000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14771000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18261000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>22764000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>18721000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>24741000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>20567000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>24166000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22919000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>21548000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>20507000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>21792000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21593000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>20521000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>19755000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>21103000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>21616000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-1090000</v>
+        <v>-5605000</v>
       </c>
       <c r="E18" s="3">
-        <v>-86000</v>
+        <v>-961000</v>
       </c>
       <c r="F18" s="3">
-        <v>283000</v>
+        <v>68000</v>
       </c>
       <c r="G18" s="3">
-        <v>-808000</v>
+        <v>570000</v>
       </c>
       <c r="H18" s="3">
-        <v>-99000</v>
+        <v>-687000</v>
       </c>
       <c r="I18" s="3">
-        <v>-149000</v>
+        <v>4000</v>
       </c>
       <c r="J18" s="3">
+        <v>532000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-345000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2792000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>780000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1162000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4171000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>329000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1023000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-83000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8049000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-401000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2964000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1353000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2204000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1259000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3380000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2350000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4175000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2227000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2710000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2875000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2978000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2630000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2530000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2206000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2183000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2282000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1797,513 +1829,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>248000</v>
+        <v>-124000</v>
       </c>
       <c r="E20" s="3">
-        <v>277000</v>
+        <v>-107000</v>
       </c>
       <c r="F20" s="3">
-        <v>308000</v>
+        <v>-136000</v>
       </c>
       <c r="G20" s="3">
-        <v>297000</v>
+        <v>-167000</v>
       </c>
       <c r="H20" s="3">
-        <v>320000</v>
+        <v>-148000</v>
       </c>
       <c r="I20" s="3">
-        <v>302000</v>
+        <v>-172000</v>
       </c>
       <c r="J20" s="3">
+        <v>-153000</v>
+      </c>
+      <c r="K20" s="3">
         <v>336000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>288000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>253000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>181000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>132000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>30000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>199000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>190000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>122000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>119000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>94000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>112000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>104000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>121000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>107000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>106000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>29000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>12000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>66000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>32000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>40000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>25000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>26000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-401000</v>
+        <v>-5037000</v>
       </c>
       <c r="E21" s="3">
-        <v>633000</v>
+        <v>-413000</v>
       </c>
       <c r="F21" s="3">
-        <v>1072000</v>
+        <v>646000</v>
       </c>
       <c r="G21" s="3">
-        <v>-44000</v>
+        <v>1218000</v>
       </c>
       <c r="H21" s="3">
-        <v>677000</v>
+        <v>-72000</v>
       </c>
       <c r="I21" s="3">
-        <v>610000</v>
+        <v>632000</v>
       </c>
       <c r="J21" s="3">
+        <v>1142000</v>
+      </c>
+      <c r="K21" s="3">
         <v>493000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2011000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1531000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-495000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3505000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>882000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1773000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>643000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7349000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>283000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2323000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-685000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1472000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1956000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2727000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2977000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4787000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2762000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3202000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3442000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3587000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3184000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3043000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2700000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2728000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2758000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>728000</v>
+      </c>
+      <c r="E22" s="3">
         <v>673000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>569000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>600000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>589000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>621000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>649000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>640000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>628000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>656000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>637000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>661000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>669000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>673000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>679000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>698000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>643000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>553000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>262000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>242000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>203000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>154000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>123000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>158000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>106000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>109000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>102000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>93000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>87000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>93000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>87000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>79000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-6224000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1515000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-378000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1100000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-400000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-496000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-649000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3132000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>377000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1618000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4700000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-310000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>549000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-572000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8625000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-925000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3423000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1503000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2342000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1177000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3427000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2333000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4046000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2133000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2586000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2839000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2917000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2583000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2462000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2145000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2103000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2203000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-50000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-76000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-23000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>21000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>538000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-251000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-71000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>176000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>217000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-376000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-539000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-178000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-11000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-186000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-459000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1028000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-862000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1332000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>10000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-485000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>184000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>622000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-230000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>390000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>362000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>868000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>773000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>713000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>566000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>472000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2403,210 +2451,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-6174000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1439000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-355000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-30000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1638000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-149000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-425000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-663000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3308000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>160000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1242000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4161000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-132000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>567000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-561000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8439000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-466000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2395000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-641000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1010000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1167000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2942000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2149000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3424000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2363000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2196000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2477000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2049000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1810000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1749000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1579000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1631000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2279000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-6170000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1439000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-343000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1636000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-149000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-414000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-634000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3275000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>193000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1219000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4140000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-109000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>587000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-537000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8420000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-449000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2376000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-628000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1010000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1166000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2942000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2147000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3422000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2361000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2196000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2474000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2047000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1808000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1749000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1577000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1631000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2706,34 +2763,37 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>24</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>5000</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>24</v>
@@ -2741,17 +2801,17 @@
       <c r="M29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O29" s="3">
         <v>-3000</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2771,8 +2831,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>24</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>24</v>
@@ -2789,11 +2849,11 @@
       <c r="AC29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE29" s="3">
         <v>1271000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>24</v>
@@ -2807,8 +2867,11 @@
       <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2908,8 +2971,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3009,210 +3075,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-248000</v>
+        <v>124000</v>
       </c>
       <c r="E32" s="3">
-        <v>-277000</v>
+        <v>107000</v>
       </c>
       <c r="F32" s="3">
-        <v>-308000</v>
+        <v>136000</v>
       </c>
       <c r="G32" s="3">
-        <v>-297000</v>
+        <v>167000</v>
       </c>
       <c r="H32" s="3">
-        <v>-320000</v>
+        <v>148000</v>
       </c>
       <c r="I32" s="3">
-        <v>-302000</v>
+        <v>172000</v>
       </c>
       <c r="J32" s="3">
+        <v>153000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-336000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-288000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-253000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-181000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-132000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-30000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-199000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-190000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-122000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-119000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-94000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-112000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-104000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-121000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-107000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-106000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>15000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-66000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-32000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6170000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1439000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-343000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1636000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-149000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-414000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-629000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3275000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>193000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1219000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4143000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-109000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>587000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-537000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8420000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-449000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2376000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-628000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1010000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1166000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2942000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2147000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3422000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2361000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2196000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2474000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3318000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1808000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1749000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1577000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3312,215 +3387,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6170000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1439000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-343000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1636000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-149000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-414000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-629000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3275000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>193000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1219000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4143000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-109000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>587000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-537000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8420000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-449000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2376000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-628000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1010000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1166000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2942000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2147000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3422000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2361000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2196000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2474000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3318000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1808000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1749000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1577000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3556,8 +3640,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3593,498 +3678,511 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9961000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10894000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6914000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12691000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6811000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7254000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10812000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14614000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13494000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10090000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7409000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8052000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9764000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8271000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7059000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7752000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10564000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>19992000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>15039000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9485000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9763000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9167000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6836000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7637000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8034000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8121000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>9235000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8813000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8569000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8737000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8190000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8801000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8986000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1727000</v>
+        <v>488000</v>
       </c>
       <c r="E42" s="3">
-        <v>615000</v>
+        <v>1706000</v>
       </c>
       <c r="F42" s="3">
-        <v>3274000</v>
+        <v>594000</v>
       </c>
       <c r="G42" s="3">
-        <v>6561000</v>
+        <v>3252000</v>
       </c>
       <c r="H42" s="3">
-        <v>6508000</v>
+        <v>6540000</v>
       </c>
       <c r="I42" s="3">
-        <v>3955000</v>
+        <v>6487000</v>
       </c>
       <c r="J42" s="3">
+        <v>3931000</v>
+      </c>
+      <c r="K42" s="3">
         <v>2606000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>763000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1358000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4873000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>8192000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>10231000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>13071000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>14861000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>17838000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>16552000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>12438000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>488000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>545000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1150000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>439000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>893000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>927000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1956000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1649000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>656000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1179000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1463000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1589000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1015000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1228000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>682000</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>12875000</v>
+        <v>12250000</v>
       </c>
       <c r="E43" s="3">
-        <v>12689000</v>
+        <v>12815000</v>
       </c>
       <c r="F43" s="3">
-        <v>11065000</v>
+        <v>12632000</v>
       </c>
       <c r="G43" s="3">
-        <v>12304000</v>
+        <v>10992000</v>
       </c>
       <c r="H43" s="3">
-        <v>12387000</v>
+        <v>12216000</v>
       </c>
       <c r="I43" s="3">
-        <v>12684000</v>
+        <v>12302000</v>
       </c>
       <c r="J43" s="3">
+        <v>12551000</v>
+      </c>
+      <c r="K43" s="3">
         <v>11305000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12144000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12549000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11555000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11378000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12332000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11767000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11234000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10051000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11722000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11478000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12725000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12471000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>14808000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>13709000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>14217000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>14364000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>13260000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>12985000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>12868000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>11397000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>11079000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>10052000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>9915000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>9260000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>9889000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>83341000</v>
+      </c>
+      <c r="E44" s="3">
         <v>85661000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>83471000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>79741000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>78972000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>78322000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>78503000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>78151000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>79777000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>79917000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>79819000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>78823000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>81897000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>81799000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>82668000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>81715000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>86961000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>83745000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>80020000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>76622000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>73279000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>68492000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>65369000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>62567000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>62038000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>61250000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>61303000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>33294000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>43031000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>42453000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>43247000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>43199000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>42680000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2918000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3282000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2843000</v>
       </c>
-      <c r="F45" s="3">
-        <v>2504000</v>
-      </c>
       <c r="G45" s="3">
+        <v>2478000</v>
+      </c>
+      <c r="H45" s="3">
         <v>2287000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2941000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2857000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2847000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3073000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2086000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2356000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2221000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2664000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4187000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4123000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4286000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5213000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2624000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2739000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3106000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2656000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3304000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2194000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2335000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2398000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2396000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2481000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2417000</v>
-      </c>
-      <c r="AE45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AF45" s="3" t="s">
         <v>24</v>
@@ -4098,412 +4196,427 @@
       <c r="AI45" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>109436000</v>
+      </c>
+      <c r="E46" s="3">
         <v>114439000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>106532000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>109275000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>106935000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>107412000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>108811000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>109523000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>109251000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>106000000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>106012000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>108666000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>116888000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>119095000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>119945000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>121642000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>131012000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>130277000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>111011000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>102229000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>101656000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>95111000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>89509000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>87830000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>87686000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>86401000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>86543000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>85194000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>64142000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>62831000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>62367000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>62488000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>62237000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1500000</v>
+        <v>1030000</v>
       </c>
       <c r="E47" s="3">
-        <v>1532000</v>
+        <v>1026000</v>
       </c>
       <c r="F47" s="3">
-        <v>1895000</v>
+        <v>1042000</v>
       </c>
       <c r="G47" s="3">
-        <v>2024000</v>
+        <v>1035000</v>
       </c>
       <c r="H47" s="3">
-        <v>2130000</v>
+        <v>1061000</v>
       </c>
       <c r="I47" s="3">
-        <v>2341000</v>
+        <v>1025000</v>
       </c>
       <c r="J47" s="3">
+        <v>969000</v>
+      </c>
+      <c r="K47" s="3">
         <v>2433000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2492000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2523000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2572000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2670000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2758000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2748000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2875000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2952000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3062000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3120000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3240000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3472000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3438000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3525000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3663000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3749000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4270000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4315000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4296000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4665000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5032000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5202000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5446000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5060000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>11287000</v>
+        <v>11236000</v>
       </c>
       <c r="E48" s="3">
-        <v>11039000</v>
+        <v>10976000</v>
       </c>
       <c r="F48" s="3">
-        <v>10661000</v>
+        <v>10696000</v>
       </c>
       <c r="G48" s="3">
+        <v>12351000</v>
+      </c>
+      <c r="H48" s="3">
         <v>10484000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10455000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10493000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10550000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10508000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10617000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10755000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10918000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11113000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11341000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11643000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13072000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11969000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12182000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12405000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13684000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13705000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13665000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13602000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12645000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12571000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12605000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12628000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12672000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12712000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12820000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12842000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12807000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12713000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10123000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10175000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10123000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10187000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10212000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10255000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10317000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10368000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10416000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10486000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10557000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10630000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9785000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9915000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9930000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10195000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10341000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10466000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>11313000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11398000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>11650000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>11812000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11465000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11269000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8252000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8044000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8083000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8132000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7867000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7914000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>7838000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>7864000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7616000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4603,8 +4716,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4704,109 +4820,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5505000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5319000</v>
       </c>
-      <c r="E52" s="3">
-        <v>5258000</v>
-      </c>
       <c r="F52" s="3">
-        <v>4994000</v>
+        <v>5190000</v>
       </c>
       <c r="G52" s="3">
-        <v>4626000</v>
+        <v>3245000</v>
       </c>
       <c r="H52" s="3">
-        <v>4522000</v>
+        <v>4562000</v>
       </c>
       <c r="I52" s="3">
-        <v>4385000</v>
+        <v>4456000</v>
       </c>
       <c r="J52" s="3">
+        <v>4320000</v>
+      </c>
+      <c r="K52" s="3">
         <v>4226000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4891000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5853000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5905000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5668000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6302000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5836000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5642000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4275000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4877000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6827000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5106000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2842000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2149000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2148000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1970000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1866000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1880000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1830000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1999000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1851000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1621000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1439000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1424000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1392000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4906,109 +5028,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>137695000</v>
+      </c>
+      <c r="E54" s="3">
         <v>142720000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>134484000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>137012000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>134281000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>134774000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>136347000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>137100000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>137558000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>135479000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>135801000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>138552000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>146846000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>148935000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>150035000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>152136000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>161261000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>162872000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>143075000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>133625000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>132598000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>126261000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>120209000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>117359000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>114659000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>113195000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>113549000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>112362000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>91007000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>90036000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>89673000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>89997000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>88950000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5044,8 +5172,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5081,614 +5210,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12267000</v>
+      </c>
+      <c r="E57" s="3">
         <v>11864000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11616000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11964000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11143000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10936000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10274000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10200000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9793000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9575000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8779000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9261000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10151000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11450000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12410000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12928000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14479000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13700000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14963000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15553000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>15101000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15267000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>14693000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12916000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>13663000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12904000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12613000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12202000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12718000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12093000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11964000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11190000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>11968000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4474000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4765000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1063000</v>
       </c>
-      <c r="F58" s="3">
-        <v>5204000</v>
-      </c>
       <c r="G58" s="3">
+        <v>5500000</v>
+      </c>
+      <c r="H58" s="3">
         <v>4891000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4609000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7926000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5190000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5431000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5406000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2591000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1296000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5377000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6534000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6021000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1693000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3634000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2922000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5173000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7340000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4354000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4357000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3381000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3190000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1389000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1611000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1981000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1335000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>988000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>720000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>367000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>384000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>632000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>80001000</v>
+        <v>57974000</v>
       </c>
       <c r="E59" s="3">
-        <v>80579000</v>
+        <v>58232000</v>
       </c>
       <c r="F59" s="3">
-        <v>78659000</v>
+        <v>59067000</v>
       </c>
       <c r="G59" s="3">
-        <v>77028000</v>
+        <v>66102000</v>
       </c>
       <c r="H59" s="3">
-        <v>76531000</v>
+        <v>56088000</v>
       </c>
       <c r="I59" s="3">
-        <v>75310000</v>
+        <v>55448000</v>
       </c>
       <c r="J59" s="3">
+        <v>54636000</v>
+      </c>
+      <c r="K59" s="3">
         <v>74662000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>74394000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>69818000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>70322000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>71435000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>70243000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>70240000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>71461000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>72659000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>74194000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>75860000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>74366000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>74419000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>72391000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>72565000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>65541000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>65484000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>64365000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>63210000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>60938000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>101620000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>40703000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>40096000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>37450000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>38560000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>35889000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>97300000</v>
+      </c>
+      <c r="E60" s="3">
         <v>96630000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>93258000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>95827000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>93062000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>92076000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>93510000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>90052000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>89618000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>84799000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>81692000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>81992000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>85771000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>88224000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>89892000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>87280000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>92307000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>92482000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>94502000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>97312000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>91846000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>92189000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>83615000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>81590000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>79417000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>77725000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>75532000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>74648000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>54409000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>52909000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>49781000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>50134000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>48489000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>53176000</v>
+      </c>
+      <c r="E61" s="3">
         <v>53162000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>46877000</v>
       </c>
-      <c r="F61" s="3">
-        <v>47103000</v>
-      </c>
       <c r="G61" s="3">
+        <v>48621000</v>
+      </c>
+      <c r="H61" s="3">
         <v>47381000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>47659000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>47465000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>51811000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51788000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51794000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>55150000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>56806000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>57042000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>57025000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>57554000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>61890000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>57325000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>58457000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>33754000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>19962000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>20298000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14859000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>11363000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10657000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10487000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10507000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10471000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9782000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9780000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10055000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10432000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9568000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>9824000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10910000</v>
+        <v>2314000</v>
       </c>
       <c r="E62" s="3">
-        <v>11365000</v>
+        <v>2212000</v>
       </c>
       <c r="F62" s="3">
-        <v>11310000</v>
+        <v>2546000</v>
       </c>
       <c r="G62" s="3">
-        <v>10555000</v>
+        <v>814000</v>
       </c>
       <c r="H62" s="3">
-        <v>10532000</v>
+        <v>2239000</v>
       </c>
       <c r="I62" s="3">
-        <v>10856000</v>
+        <v>2158000</v>
       </c>
       <c r="J62" s="3">
+        <v>2198000</v>
+      </c>
+      <c r="K62" s="3">
         <v>11085000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13787000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13677000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14227000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14600000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>18299000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>20171000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>20430000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>21041000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>23182000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>23315000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>24179000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>24651000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>24263000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>24156000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>24999000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>24702000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>25964000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>26337000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>26248000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>26219000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>25673000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>29050000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>29305000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>29418000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>28487000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5788,8 +5936,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5889,8 +6040,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5990,109 +6144,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>160696000</v>
+        <v>161257000</v>
       </c>
       <c r="E66" s="3">
-        <v>151493000</v>
+        <v>160702000</v>
       </c>
       <c r="F66" s="3">
-        <v>154245000</v>
+        <v>151500000</v>
       </c>
       <c r="G66" s="3">
-        <v>151010000</v>
+        <v>154240000</v>
       </c>
       <c r="H66" s="3">
-        <v>150291000</v>
+        <v>150998000</v>
       </c>
       <c r="I66" s="3">
-        <v>151855000</v>
+        <v>150267000</v>
       </c>
       <c r="J66" s="3">
+        <v>151831000</v>
+      </c>
+      <c r="K66" s="3">
         <v>152983000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>155257000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>150367000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>151199000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>153551000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>161286000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>165617000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>168093000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>170452000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>173082000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>174539000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>152740000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>142242000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>136714000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>131583000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>120084000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>117020000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>115948000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>114636000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>112327000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>110706000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>89921000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>92073000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>89578000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>89180000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>86861000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6128,8 +6288,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6229,8 +6390,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6330,8 +6494,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6431,8 +6598,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6532,109 +6702,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19299000</v>
+      </c>
+      <c r="E72" s="3">
         <v>25469000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>26908000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>27251000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>27274000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28910000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>29059000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>29473000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>30107000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>33382000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>33189000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>34408000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>38551000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>38660000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>38073000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>38610000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>47029000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>47478000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>49854000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>50644000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>53986000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>52819000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>58090000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>55941000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>54666000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>52303000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>52095000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>49618000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>44052000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>42222000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>42165000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>40714000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>40641000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6734,8 +6910,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6835,8 +7014,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6936,109 +7118,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-23552000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-17976000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-17009000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-17233000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-16729000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-15517000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-15508000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-15883000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-17699000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-14888000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-15398000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-14999000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-14440000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-16682000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-18058000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-18316000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-11821000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-11667000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-9665000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-8617000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-4116000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-5322000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>125000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>339000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-1289000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-1441000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1222000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1656000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1086000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-2037000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>95000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>817000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2089000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7138,215 +7326,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6170000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1439000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-343000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1636000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-149000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-414000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-629000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3275000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>193000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1219000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4143000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-109000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>587000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-537000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8420000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-449000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2376000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-628000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1010000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1166000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2942000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2147000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3422000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2361000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2196000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2474000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3318000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1808000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1749000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1577000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7382,109 +7579,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>441000</v>
+        <v>467000</v>
       </c>
       <c r="E83" s="3">
-        <v>442000</v>
+        <v>456000</v>
       </c>
       <c r="F83" s="3">
-        <v>481000</v>
+        <v>457000</v>
       </c>
       <c r="G83" s="3">
-        <v>467000</v>
+        <v>261000</v>
       </c>
       <c r="H83" s="3">
-        <v>456000</v>
+        <v>493000</v>
       </c>
       <c r="I83" s="3">
-        <v>457000</v>
+        <v>498000</v>
       </c>
       <c r="J83" s="3">
+        <v>486000</v>
+      </c>
+      <c r="K83" s="3">
         <v>502000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>493000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>498000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>486000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>534000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>523000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>551000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>536000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>578000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>565000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>547000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>556000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>628000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>576000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>546000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>521000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>583000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>523000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>507000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>501000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>582000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>522000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>494000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>471000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>546000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>474000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7584,8 +7785,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7685,8 +7889,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7786,8 +7993,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7887,8 +8097,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7988,109 +8201,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1345000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3923000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3362000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3381000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>22000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2875000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-318000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3457000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3190000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>81000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3216000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>716000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-262000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-483000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3387000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4009000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4819000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5280000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4302000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2220000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2424000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-590000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2788000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2947000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4559000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4680000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3136000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2903000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3396000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4949000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2098000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2832000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3202000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8126,109 +8345,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-492000</v>
+        <v>-611000</v>
       </c>
       <c r="E91" s="3">
+        <v>-404000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-567000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-431000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-332000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-296000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-468000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-326000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-284000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-263000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-349000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-222000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-245000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-222000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-291000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-265000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-262000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-348000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-428000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-447000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-465000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-421000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-501000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-495000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-457000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-376000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-394000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-435000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-399000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-439000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-932000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-599000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-595000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8328,8 +8551,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8429,109 +8655,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>679000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2100000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2074000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2804000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-403000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3015000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1823000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2151000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>290000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3266000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2965000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1935000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2966000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1659000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2764000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1543000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4137000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12307000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-379000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>517000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1194000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-86000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-767000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2424000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-902000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1414000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>119000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-457000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-218000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1123000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-260000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1416000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-614000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8567,31 +8799,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8624,52 +8857,55 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-1158000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1157000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-1156000</v>
       </c>
       <c r="X96" s="3">
         <v>-1156000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-1156000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1161000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-970000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-979000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-991000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-842000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-855000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-852000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-868000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-672000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-676000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8769,8 +9005,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8870,8 +9109,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8971,307 +9213,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300000</v>
+      </c>
+      <c r="E100" s="3">
         <v>10000000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4462000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-356000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-38000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3413000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1680000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-250000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-602000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-396000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4362000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1171000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-48000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2681000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-468000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>22462000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>10280000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1403000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4240000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2919000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2823000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-856000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3689000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4332000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2845000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2241000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3335000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3311000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2463000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1574000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2204000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>3000</v>
+        <v>-24000</v>
       </c>
       <c r="E101" s="3">
-        <v>-28000</v>
+        <v>-8000</v>
       </c>
       <c r="F101" s="3">
-        <v>52000</v>
+        <v>10000</v>
       </c>
       <c r="G101" s="3">
-        <v>-24000</v>
+        <v>61000</v>
       </c>
       <c r="H101" s="3">
-        <v>-8000</v>
+        <v>-63000</v>
       </c>
       <c r="I101" s="3">
-        <v>10000</v>
+        <v>-68000</v>
       </c>
       <c r="J101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="K101" s="3">
         <v>61000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-63000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-68000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-20000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-18000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>59000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>37000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>36000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-47000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>22000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-25000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-44000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>8000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>7000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>21000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>32000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>20000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-27000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-933000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3980000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5778000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5881000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-443000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3811000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1117000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3399000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2677000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-650000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1716000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1513000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1161000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-689000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2812000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-9387000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4911000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5552000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-278000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>597000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2240000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-801000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-349000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-33000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1110000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>418000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>212000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>547000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-605000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-185000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>381000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>BA</t>
   </si>
@@ -656,447 +656,459 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15242000</v>
+      </c>
+      <c r="E8" s="3">
         <v>17840000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16866000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16569000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22018000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18104000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19751000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17921000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19980000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15956000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16681000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13991000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14793000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15278000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16998000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15217000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15802000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14139000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11807000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16908000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>20560000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>19980000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>21361000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>22917000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>28341000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>25146000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>24258000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>23382000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>24770000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>24223000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>23051000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>21961000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>23286000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>23898000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>16784000</v>
+      </c>
+      <c r="E9" s="3">
         <v>21347000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15637000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14613000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>19173000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16939000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>17812000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15493000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18124000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16778000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14559000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13645000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17307000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13566000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14588000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13808000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>20992000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13105000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12978000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>16768000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>18708000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>16930000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>17810000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>18645000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>22090000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>21040000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>19536000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>18824000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>19881000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>19956000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>18702000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>18073000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>19464000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>19904000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-1542000</v>
+      </c>
+      <c r="E10" s="3">
         <v>-3507000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1229000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1956000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2845000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1165000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1939000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2428000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1856000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-822000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2122000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>346000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-2514000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1712000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2410000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1409000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-5190000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1034000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-1171000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>140000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1852000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3050000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3551000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4272000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6251000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4106000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4722000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4558000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4889000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4267000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4349000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3888000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3822000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3994000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1133,112 +1145,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>836000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1154000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>954000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>868000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>881000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>958000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>797000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>741000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>794000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>727000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>698000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>633000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>678000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>575000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>497000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>499000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>605000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>574000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>625000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>672000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>749000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>778000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>826000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>866000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>852000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>826000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>827000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>764000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>762000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>768000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>813000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>836000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>726000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>857000</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,40 +1357,43 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E14" s="3">
         <v>15000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-5000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>80000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>147000</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>532000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>24</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>24</v>
@@ -1391,11 +1410,11 @@
       <c r="R14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T14" s="3">
         <v>498000</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>24</v>
@@ -1403,17 +1422,17 @@
       <c r="V14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X14" s="3">
         <v>2649000</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5610000</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>24</v>
@@ -1424,8 +1443,8 @@
       <c r="AC14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1445,35 +1464,38 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>509000</v>
+      </c>
+      <c r="E15" s="3">
         <v>444000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>441000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>442000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>481000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>467000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>456000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>457000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1549,8 +1571,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1584,216 +1609,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>18892000</v>
+      </c>
+      <c r="E17" s="3">
         <v>23445000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17827000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16501000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21448000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18791000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19747000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17389000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20325000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18748000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15901000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15153000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18964000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14949000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15975000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15300000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23851000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14540000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14771000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18261000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22764000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18721000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>24741000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>20567000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>24166000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>22919000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>21548000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>20507000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21792000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>21593000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>20521000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>19755000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>21103000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>21616000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-3650000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5605000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-961000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>68000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>570000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-687000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>532000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-345000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2792000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>780000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1162000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4171000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>329000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1023000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-83000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8049000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-401000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2964000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1353000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2204000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1259000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3380000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2350000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4175000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2227000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2710000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2875000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2978000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2630000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2530000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2206000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2183000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2282000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1830,528 +1862,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-306000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-124000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-107000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-136000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-167000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-148000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-172000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-153000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>336000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>288000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>253000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>181000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>132000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>30000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>199000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>190000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>122000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>119000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>94000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>112000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>104000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>121000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>107000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>106000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>29000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>12000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>66000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>32000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>40000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>25000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>26000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-2835000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5037000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-413000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>646000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1218000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-72000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>632000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1142000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>493000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2011000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1531000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-495000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3505000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>882000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1773000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>643000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7349000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>283000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2323000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-685000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1472000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1956000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2727000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2977000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4787000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2762000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3202000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3442000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3587000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3184000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3043000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2700000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2728000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2758000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>755000</v>
+      </c>
+      <c r="E22" s="3">
         <v>728000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>673000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>569000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>600000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>589000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>621000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>649000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>640000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>628000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>656000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>637000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>661000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>669000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>673000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>679000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>698000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>643000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>553000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>262000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>242000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>203000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>154000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>123000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>158000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>106000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>109000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>102000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>93000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>87000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>93000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>87000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>79000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-4093000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6224000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1515000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-378000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1100000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-400000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-496000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-649000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3132000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>377000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1618000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4700000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-310000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>549000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-572000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8625000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-925000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3423000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1503000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2342000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1177000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3427000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2333000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4046000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2133000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2586000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2839000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2917000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2583000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2462000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2145000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2103000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2203000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-232000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-50000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-76000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-23000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>21000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>538000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-251000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-71000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>176000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>217000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-376000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-539000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-178000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-18000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-11000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-186000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-459000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1028000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-862000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1332000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>10000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-485000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>184000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>622000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-230000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>390000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>362000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>868000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>773000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>713000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>566000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>472000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2454,216 +2502,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-3861000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6174000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1439000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-355000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-30000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1638000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-149000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-425000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-663000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3308000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>160000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1242000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4161000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-132000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>567000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-561000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8439000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-466000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2395000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-641000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1010000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1167000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2942000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2149000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3424000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2363000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2196000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2477000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2049000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1810000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1749000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1579000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1631000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2279000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-3923000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6170000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1439000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-343000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-23000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1636000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-149000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-414000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-634000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3275000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>193000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1219000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4140000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-109000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>587000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-537000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8420000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-449000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2376000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-628000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1010000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1166000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2942000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2147000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3422000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2361000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2196000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2474000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2047000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1808000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1749000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1577000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1631000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2766,8 +2823,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2793,10 +2853,10 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>5000</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
@@ -2804,17 +2864,17 @@
       <c r="N29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P29" s="3">
         <v>-3000</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2834,8 +2894,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>24</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>24</v>
@@ -2852,11 +2912,11 @@
       <c r="AD29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF29" s="3">
         <v>1271000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>24</v>
@@ -2870,8 +2930,11 @@
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2974,8 +3037,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3078,216 +3144,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>306000</v>
+      </c>
+      <c r="E32" s="3">
         <v>124000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>107000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>136000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>167000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>148000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>172000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>153000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-336000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-288000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-253000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-181000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-132000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-199000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-190000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-122000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-119000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-94000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-112000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-104000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-121000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-107000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-106000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>15000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-66000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-32000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3865000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6170000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1439000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-343000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1636000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-149000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-414000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-629000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3275000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>193000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1219000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4143000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-109000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>587000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-537000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8420000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-449000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2376000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-628000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1010000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1166000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2942000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2147000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3422000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2361000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2196000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2474000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3318000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1808000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1749000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1577000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3390,221 +3465,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3865000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6170000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1439000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-343000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1636000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-149000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-414000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-629000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3275000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>193000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1219000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4143000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-109000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>587000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-537000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8420000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-449000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2376000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-628000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1010000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1166000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2942000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2147000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3422000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2361000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2196000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2474000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3318000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1808000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1749000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1577000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3641,8 +3725,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3679,513 +3764,526 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13801000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9961000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10894000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6914000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12691000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6811000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7254000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10812000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14614000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13494000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10090000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7409000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8052000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9764000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8271000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7059000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7752000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10564000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19992000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>15039000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9485000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9763000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9167000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6836000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7637000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8034000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8121000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>9235000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8813000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8569000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8737000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8190000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8801000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8986000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12460000</v>
+      </c>
+      <c r="E42" s="3">
         <v>488000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1706000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>594000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3252000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6540000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6487000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3931000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2606000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>763000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1358000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4873000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>8192000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>10231000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>13071000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>14861000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>17838000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>16552000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>12438000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>488000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>545000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1150000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>439000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>893000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>927000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1956000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1649000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>656000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1179000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1463000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1589000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1015000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1228000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>682000</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11024000</v>
+      </c>
+      <c r="E43" s="3">
         <v>12250000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12815000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12632000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10992000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12216000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12302000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12551000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11305000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12144000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12549000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11555000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11378000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12332000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11767000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11234000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10051000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11722000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11478000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12725000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>12471000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>14808000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>13709000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>14217000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>14364000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>13260000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>12985000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>12868000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>11397000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>11079000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>10052000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>9915000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>9260000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>9889000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>87550000</v>
+      </c>
+      <c r="E44" s="3">
         <v>83341000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>85661000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>83471000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>79741000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>78972000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>78322000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>78503000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>78151000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>79777000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>79917000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>79819000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>78823000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>81897000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>81799000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>82668000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>81715000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>86961000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>83745000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>80020000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>76622000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>73279000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>68492000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>65369000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>62567000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>62038000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>61250000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>61303000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>33294000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>43031000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>42453000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>43247000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>43199000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>42680000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2935000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2918000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3282000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2843000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2478000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2287000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2941000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2857000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2847000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3073000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2086000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2356000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2221000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2664000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4187000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4123000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4286000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5213000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2624000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2739000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3106000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2656000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3304000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2194000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2335000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2398000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2396000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2481000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2417000</v>
-      </c>
-      <c r="AF45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AG45" s="3" t="s">
         <v>24</v>
@@ -4199,424 +4297,439 @@
       <c r="AJ45" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>127998000</v>
+      </c>
+      <c r="E46" s="3">
         <v>109436000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>114439000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>106532000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>109275000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>106935000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>107412000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>108811000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>109523000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>109251000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>106000000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>106012000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>108666000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>116888000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>119095000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>119945000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>121642000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>131012000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>130277000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>111011000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>102229000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>101656000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>95111000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>89509000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>87830000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>87686000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>86401000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>86543000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>85194000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>64142000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>62831000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>62367000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>62488000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>62237000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>999000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1030000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1026000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1042000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1035000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1061000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1025000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>969000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2433000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2492000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2523000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2572000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2670000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2758000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2748000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2875000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2952000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3062000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3120000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3240000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3472000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3438000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3525000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3663000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3749000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4270000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4315000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4296000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4665000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5032000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5202000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5446000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5060000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13396000</v>
+      </c>
+      <c r="E48" s="3">
         <v>11236000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10976000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10696000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12351000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10484000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10455000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10493000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10550000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10508000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10617000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10755000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10918000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11113000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11341000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11643000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13072000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11969000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12182000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12405000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13684000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13705000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13665000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13602000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12645000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12571000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12605000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12628000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12672000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12712000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12820000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12842000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12807000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12713000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10041000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10123000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10175000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10123000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10187000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10212000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10255000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10317000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10368000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10416000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10486000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10557000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10630000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9785000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9915000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9930000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10195000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10341000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10466000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11313000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>11398000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>11650000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11812000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11465000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11269000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8252000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8044000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8083000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>8132000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7867000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>7914000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>7838000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7864000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7616000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4719,8 +4832,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4823,112 +4939,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3430000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5505000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5319000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5190000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3245000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4562000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4456000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4320000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4226000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4891000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5853000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5905000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5668000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6302000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5836000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5642000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4275000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4877000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6827000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5106000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2842000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2149000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2148000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1970000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1866000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1880000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1830000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1999000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1851000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1621000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1439000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1424000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1392000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5031,112 +5153,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>156363000</v>
+      </c>
+      <c r="E54" s="3">
         <v>137695000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>142720000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>134484000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>137012000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>134281000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>134774000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>136347000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>137100000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>137558000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>135479000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>135801000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>138552000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>146846000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>148935000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>150035000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>152136000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>161261000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>162872000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>143075000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>133625000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>132598000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>126261000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>120209000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>117359000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>114659000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>113195000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>113549000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>112362000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>91007000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>90036000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>89673000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>89997000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>88950000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5173,8 +5301,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5211,632 +5340,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11364000</v>
+      </c>
+      <c r="E57" s="3">
         <v>12267000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11864000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11616000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11964000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11143000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10936000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10274000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10200000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9793000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9575000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8779000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9261000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10151000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11450000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12410000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12928000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14479000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13700000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14963000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>15553000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15101000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15267000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>14693000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12916000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>13663000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12904000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12613000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12202000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12718000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12093000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11964000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>11190000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>11968000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1602000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4474000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4765000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1063000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5500000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4891000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4609000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7926000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5190000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5431000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5406000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2591000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1296000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5377000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6534000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6021000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1693000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3634000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2922000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5173000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7340000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4354000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4357000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3381000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3190000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1389000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1611000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1981000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1335000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>988000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>720000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>367000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>384000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>632000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>72293000</v>
+      </c>
+      <c r="E59" s="3">
         <v>57974000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>58232000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>59067000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>66102000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>56088000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>55448000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>54636000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>74662000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>74394000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>69818000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>70322000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>71435000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>70243000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>70240000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>71461000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>72659000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>74194000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>75860000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>74366000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>74419000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>72391000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>72565000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>65541000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>65484000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>64365000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>63210000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>60938000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>101620000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>40703000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>40096000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>37450000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>38560000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>35889000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>97078000</v>
+      </c>
+      <c r="E60" s="3">
         <v>97300000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>96630000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>93258000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>95827000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>93062000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>92076000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>93510000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>90052000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>89618000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>84799000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>81692000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>81992000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>85771000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>88224000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>89892000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>87280000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>92307000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>92482000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>94502000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>97312000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>91846000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>92189000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>83615000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>81590000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>79417000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>77725000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>75532000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>74648000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>54409000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>52909000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>49781000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>50134000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>48489000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>54356000</v>
+      </c>
+      <c r="E61" s="3">
         <v>53176000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>53162000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>46877000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>48621000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>47381000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>47659000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>47465000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51811000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51788000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>51794000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>55150000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>56806000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>57042000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>57025000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>57554000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>61890000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>57325000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>58457000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>33754000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>19962000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>20298000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14859000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>11363000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10657000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10487000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10507000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10471000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9782000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9780000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10055000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10432000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>9568000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9824000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>548000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2314000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2212000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2546000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>814000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2239000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2158000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2198000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11085000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13787000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13677000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14227000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14600000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18299000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>20171000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20430000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>21041000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>23182000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>23315000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>24179000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>24651000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>24263000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>24156000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>24999000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>24702000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>25964000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>26337000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>26248000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>26219000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>25673000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>29050000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>29305000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>29418000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>28487000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5939,8 +6087,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6043,8 +6194,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6147,112 +6301,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>160277000</v>
+      </c>
+      <c r="E66" s="3">
         <v>161257000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>160702000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>151500000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>154240000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>150998000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>150267000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>151831000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>152983000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>155257000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>150367000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>151199000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>153551000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>161286000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>165617000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>168093000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>170452000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>173082000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>174539000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>152740000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>142242000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>136714000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>131583000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>120084000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>117020000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>115948000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>114636000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>112327000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>110706000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>89921000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>92073000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>89578000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>89180000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>86861000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6289,8 +6449,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6393,8 +6554,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6497,13 +6661,16 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -6601,8 +6768,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6705,112 +6875,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15362000</v>
+      </c>
+      <c r="E72" s="3">
         <v>19299000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25469000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>26908000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>27251000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>27274000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>28910000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>29059000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>29473000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>30107000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>33382000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>33189000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>34408000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>38551000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>38660000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>38073000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>38610000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>47029000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>47478000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>49854000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>50644000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>53986000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>52819000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>58090000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>55941000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>54666000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>52303000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>52095000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>49618000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>44052000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>42222000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>42165000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>40714000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>40641000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6913,8 +7089,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7017,8 +7196,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7121,112 +7303,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-3914000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-23552000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-17976000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-17009000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-17233000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-16729000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-15517000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-15508000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-15883000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-17699000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-14888000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-15398000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-14999000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-14440000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-16682000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-18058000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-18316000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-11821000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-11667000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-9665000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-8617000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-4116000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-5322000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>125000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>339000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-1289000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-1441000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1222000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1656000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1086000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-2037000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>95000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>817000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2089000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7329,221 +7517,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3865000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6170000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1439000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-343000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1636000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-149000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-414000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-629000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3275000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>193000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1219000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4143000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-109000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>587000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-537000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8420000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-449000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2376000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-628000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1010000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1166000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2942000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2147000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3422000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2361000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2196000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2474000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3318000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1808000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1749000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1577000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7580,112 +7777,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E83" s="3">
         <v>467000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>456000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>457000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>261000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>493000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>498000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>486000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>502000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>493000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>498000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>486000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>534000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>523000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>551000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>536000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>578000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>565000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>547000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>556000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>628000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>576000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>546000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>521000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>583000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>523000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>507000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>501000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>582000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>522000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>494000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>471000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>546000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>474000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7788,8 +7989,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7892,8 +8096,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7996,8 +8203,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8100,8 +8310,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8204,112 +8417,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3450000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1345000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3923000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3362000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3381000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>22000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2875000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-318000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3457000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3190000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>81000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3216000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>716000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-262000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-483000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3387000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4009000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4819000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-5280000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4302000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2220000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2424000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-590000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2788000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2947000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4559000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4680000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3136000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2903000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3396000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4949000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2098000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2832000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3202000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8346,112 +8565,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-648000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-611000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-404000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-567000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-431000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-332000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-296000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-468000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-326000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-284000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-263000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-349000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-222000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-245000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-222000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-291000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-265000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-262000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-348000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-428000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-447000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-465000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-421000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-501000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-495000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-457000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-376000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-394000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-435000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-399000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-439000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-932000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-599000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-595000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8554,8 +8777,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8658,112 +8884,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12626000</v>
+      </c>
+      <c r="E94" s="3">
         <v>679000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2100000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2074000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2804000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-403000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3015000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1823000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2151000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>290000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>3266000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2965000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1935000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2966000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1659000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2764000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1543000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4137000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12307000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-379000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>517000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1194000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-86000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-767000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2424000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-902000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1414000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>119000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-457000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-218000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1123000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-260000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1416000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-614000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8800,8 +9032,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8826,8 +9059,8 @@
       <c r="J96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8860,52 +9093,55 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-1158000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1157000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-1156000</v>
       </c>
       <c r="Y96" s="3">
         <v>-1156000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-1156000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-1161000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-970000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-979000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-991000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-842000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-855000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-852000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-868000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-672000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-676000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9008,8 +9244,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9112,8 +9351,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9216,316 +9458,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>19971000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>10000000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4462000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-356000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-38000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3413000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1680000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-250000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-18000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-602000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-396000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4362000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1171000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-19000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-48000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2681000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-468000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>22462000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>10280000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1403000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4240000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2919000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2823000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-856000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3689000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4332000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2845000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2241000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3335000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3311000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2463000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1574000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2204000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-24000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>10000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>61000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-63000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-68000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>61000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-63000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-68000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-18000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>59000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>37000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>36000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-47000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>22000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-44000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>8000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>7000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>21000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>32000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>20000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-27000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3840000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-933000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3980000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5778000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5881000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-443000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3811000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1117000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3399000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2677000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-650000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1716000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1513000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1161000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-689000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2812000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9387000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4911000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5552000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-278000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>597000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2240000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-801000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-349000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-33000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1110000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>418000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>212000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>547000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-605000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-185000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>381000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>BA</t>
   </si>
@@ -656,459 +656,471 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>19496000</v>
+      </c>
+      <c r="E8" s="3">
         <v>15242000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17840000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16866000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16569000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22018000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>18104000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19751000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17921000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19980000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15956000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16681000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13991000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14793000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15278000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16998000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15217000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15802000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14139000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11807000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16908000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>20560000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>19980000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>21361000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>22917000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>28341000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>25146000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>24258000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>23382000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>24770000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>24223000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>23051000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>21961000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>23286000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>23898000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>17049000</v>
+      </c>
+      <c r="E9" s="3">
         <v>16784000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>21347000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15637000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14613000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>19173000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16939000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>17812000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15493000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18124000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16778000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14559000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13645000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>17307000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13566000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14588000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13808000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>20992000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13105000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12978000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>16768000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>18708000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>16930000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>17810000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>18645000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>22090000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>21040000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>19536000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>18824000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>19881000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>19956000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>18702000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>18073000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>19464000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>19904000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2447000</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1542000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-3507000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1229000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1956000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2845000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1165000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1939000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2428000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1856000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-822000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2122000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>346000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-2514000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1712000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2410000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1409000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-5190000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1034000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-1171000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>140000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1852000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3050000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3551000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4272000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>6251000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4106000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4722000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4558000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4889000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4267000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4349000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3888000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3822000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3994000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1146,115 +1158,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>844000</v>
+      </c>
+      <c r="E12" s="3">
         <v>836000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1154000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>954000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>868000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>881000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>958000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>797000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>741000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>794000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>727000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>698000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>633000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>678000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>575000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>497000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>499000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>605000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>574000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>625000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>672000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>749000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>778000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>826000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>866000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>852000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>826000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>827000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>764000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>762000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>768000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>813000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>836000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>726000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>857000</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1360,43 +1376,46 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E14" s="3">
         <v>6000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>15000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-5000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>80000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>147000</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>532000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>24</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>24</v>
@@ -1413,11 +1432,11 @@
       <c r="S14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U14" s="3">
         <v>498000</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>24</v>
@@ -1425,17 +1444,17 @@
       <c r="W14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y14" s="3">
         <v>2649000</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5610000</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>24</v>
@@ -1446,8 +1465,8 @@
       <c r="AD14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1467,38 +1486,41 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>466000</v>
+      </c>
+      <c r="E15" s="3">
         <v>509000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>444000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>441000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>442000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>481000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>467000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>456000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>457000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1574,8 +1596,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1610,222 +1635,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>18957000</v>
+      </c>
+      <c r="E17" s="3">
         <v>18892000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23445000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17827000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16501000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21448000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18791000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19747000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17389000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20325000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18748000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15901000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15153000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18964000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14949000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15975000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15300000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23851000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14540000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14771000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>18261000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22764000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>18721000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>24741000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>20567000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>24166000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>22919000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>21548000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>20507000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>21792000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>21593000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>20521000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>19755000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>21103000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>21616000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>539000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3650000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5605000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-961000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>68000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>570000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-687000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>532000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-345000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2792000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>780000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1162000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4171000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>329000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1023000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-83000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8049000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-401000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2964000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1353000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2204000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1259000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3380000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2350000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4175000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2227000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2710000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2875000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2978000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2630000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2530000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2206000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2183000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2282000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1863,543 +1895,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-275000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-306000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-124000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-107000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-136000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-167000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-148000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-172000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-153000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>336000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>288000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>253000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>181000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>132000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>30000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>199000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>190000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>122000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>119000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>94000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>112000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>104000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>121000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>107000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>106000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>29000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>12000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>66000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>32000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>40000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>25000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2835000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5037000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-413000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>646000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1218000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-72000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>632000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1142000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>493000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2011000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1531000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-495000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3505000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>882000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1773000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>643000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7349000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>283000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2323000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-685000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1472000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1956000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2727000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2977000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4787000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2762000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3202000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3442000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3587000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3184000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3043000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2700000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2728000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2758000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>708000</v>
+      </c>
+      <c r="E22" s="3">
         <v>755000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>728000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>673000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>569000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>600000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>589000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>621000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>649000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>640000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>628000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>656000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>637000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>661000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>669000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>673000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>679000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>698000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>643000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>553000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>262000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>242000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>203000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>154000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>123000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>158000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>106000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>109000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>102000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>93000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>87000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>93000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>87000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>79000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4093000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6224000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1515000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-378000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1100000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-400000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-496000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-649000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3132000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>377000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1618000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4700000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-310000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>549000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-572000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8625000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-925000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3423000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1503000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2342000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1177000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3427000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2333000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4046000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2133000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2586000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2839000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2917000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2583000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2462000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2145000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2103000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2203000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-232000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-50000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-76000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-23000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>538000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-251000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-71000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>176000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>217000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-376000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-539000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-178000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-18000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-11000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-186000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-459000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1028000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-862000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1332000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>10000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-485000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>184000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>622000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-230000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>390000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>362000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>868000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>773000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>713000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>566000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>472000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2505,222 +2553,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3861000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6174000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1439000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-355000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-30000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1638000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-149000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-425000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-663000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3308000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>160000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1242000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4161000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-132000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>567000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-561000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8439000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-466000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2395000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-641000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1010000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1167000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2149000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3424000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2363000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2196000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2477000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2049000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1810000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1749000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1579000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1631000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2279000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3923000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6170000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1439000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-343000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-23000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1636000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-149000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-414000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-634000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3275000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>193000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1219000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4140000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-109000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>587000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-537000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8420000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-449000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2376000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-628000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1010000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1166000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2147000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3422000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2361000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2196000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2474000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2047000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1808000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1749000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1577000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1631000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2826,8 +2883,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2856,10 +2916,10 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>5000</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>24</v>
@@ -2867,17 +2927,17 @@
       <c r="O29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-3000</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2897,8 +2957,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>24</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>24</v>
@@ -2915,11 +2975,11 @@
       <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG29" s="3">
         <v>1271000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>24</v>
@@ -2933,8 +2993,11 @@
       <c r="AK29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3040,8 +3103,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3147,222 +3213,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E32" s="3">
         <v>306000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>124000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>107000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>136000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>167000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>148000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>172000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>153000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-336000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-288000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-253000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-181000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-132000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-30000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-199000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-190000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-122000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-119000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-94000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-112000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-104000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-121000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-107000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-106000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>15000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-66000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-32000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3865000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6170000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1439000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-343000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-23000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1636000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-149000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-414000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-629000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3275000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>193000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1219000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4143000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-109000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>587000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-537000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8420000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-449000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2376000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-628000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1010000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1166000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2147000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3422000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2361000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2196000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2474000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3318000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1808000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1749000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1577000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3468,227 +3543,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3865000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6170000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1439000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-343000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-23000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1636000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-149000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-414000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-629000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3275000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>193000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1219000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4143000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-109000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>587000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-537000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8420000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-449000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2376000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-628000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1010000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1166000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2147000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3422000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2361000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2196000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2474000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3318000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1808000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1749000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1577000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3726,8 +3810,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3765,528 +3850,541 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10142000</v>
+      </c>
+      <c r="E41" s="3">
         <v>13801000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9961000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10894000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6914000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12691000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6811000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7254000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10812000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14614000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13494000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10090000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7409000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8052000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9764000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8271000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7059000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7752000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10564000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>19992000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>15039000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9485000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9763000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9167000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6836000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7637000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8034000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8121000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>9235000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8813000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8569000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8737000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8190000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8801000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>8986000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13511000</v>
+      </c>
+      <c r="E42" s="3">
         <v>12460000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>488000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1706000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>594000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3252000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6540000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6487000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3931000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2606000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>763000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1358000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4873000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>8192000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>10231000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>13071000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>14861000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>17838000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>16552000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>12438000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>488000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>545000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1150000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>439000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>893000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>927000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1956000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1649000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>656000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1179000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1463000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1589000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1015000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1228000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>682000</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12235000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11024000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12250000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12815000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12632000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10992000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12216000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12302000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12551000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11305000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12144000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12549000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11555000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11378000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12332000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11767000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11234000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10051000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11722000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11478000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>12725000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>12471000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>14808000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>13709000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>14217000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>14364000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>13260000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>12985000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>12868000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>11397000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>11079000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>10052000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>9915000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>9260000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>9889000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>89077000</v>
+      </c>
+      <c r="E44" s="3">
         <v>87550000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>83341000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>85661000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>83471000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>79741000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>78972000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>78322000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>78503000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>78151000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>79777000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>79917000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>79819000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>78823000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>81897000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>81799000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>82668000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>81715000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>86961000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>83745000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>80020000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>76622000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>73279000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>68492000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>65369000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>62567000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>62038000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>61250000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>61303000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>33294000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>43031000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>42453000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>43247000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>43199000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>42680000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2474000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2935000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2918000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3282000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2843000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2478000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2287000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2941000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2857000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2847000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3073000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2086000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2356000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2221000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2664000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4187000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4123000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4286000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5213000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2624000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2739000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3106000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2656000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3304000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2194000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2335000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2398000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2396000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2481000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2417000</v>
-      </c>
-      <c r="AG45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AH45" s="3" t="s">
         <v>24</v>
@@ -4300,436 +4398,451 @@
       <c r="AK45" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>127662000</v>
+      </c>
+      <c r="E46" s="3">
         <v>127998000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>109436000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>114439000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>106532000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>109275000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>106935000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>107412000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>108811000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>109523000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>109251000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>106000000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>106012000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>108666000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>116888000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>119095000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>119945000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>121642000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>131012000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>130277000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>111011000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>102229000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>101656000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>95111000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>89509000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>87830000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>87686000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>86401000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>86543000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>85194000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>64142000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>62831000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>62367000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>62488000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>62237000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1001000</v>
+      </c>
+      <c r="E47" s="3">
         <v>999000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1030000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1026000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1042000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1035000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1061000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1025000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>969000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2433000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2492000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2523000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2572000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2670000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2758000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2748000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2875000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2952000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3062000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3120000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3240000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3472000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3438000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3525000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3663000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3749000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4270000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4315000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4296000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4665000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5032000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5202000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5446000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5060000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11459000</v>
+      </c>
+      <c r="E48" s="3">
         <v>13396000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11236000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10976000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10696000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12351000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10484000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10455000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10493000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10550000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10508000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10617000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10755000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10918000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11113000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11341000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11643000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13072000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11969000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12182000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12405000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13684000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13705000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13665000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13602000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12645000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12571000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12605000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12628000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12672000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12712000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12820000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12842000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12807000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12713000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9995000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10041000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10123000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10175000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10123000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10187000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10212000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10255000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10317000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10368000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10416000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10486000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10557000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10630000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9785000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9915000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9930000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10195000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10341000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10466000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>11313000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>11398000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11650000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11812000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11465000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11269000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8252000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8044000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>8083000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8132000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>7867000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>7914000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7838000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7864000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7616000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4835,8 +4948,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4942,115 +5058,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5932000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3430000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5505000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5319000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5190000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3245000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4562000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4456000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4320000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4226000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4891000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5853000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5905000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5668000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6302000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5836000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5642000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4275000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4877000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6827000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5106000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2842000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2149000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2148000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1970000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1866000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1880000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1830000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1999000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1851000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1621000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1439000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1424000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1392000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5156,115 +5278,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>156494000</v>
+      </c>
+      <c r="E54" s="3">
         <v>156363000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>137695000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>142720000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>134484000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>137012000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>134281000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>134774000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>136347000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>137100000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>137558000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>135479000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>135801000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>138552000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>146846000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>148935000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>150035000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>152136000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>161261000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>162872000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>143075000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>133625000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>132598000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>126261000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>120209000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>117359000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>114659000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>113195000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>113549000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>112362000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>91007000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>90036000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>89673000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>89997000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>88950000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5302,8 +5430,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5341,650 +5470,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11034000</v>
+      </c>
+      <c r="E57" s="3">
         <v>11364000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12267000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11864000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11616000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11964000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11143000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10936000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10274000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10200000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9793000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9575000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8779000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9261000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10151000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11450000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12410000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12928000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14479000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>13700000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>14963000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15553000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15101000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>15267000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>14693000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12916000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>13663000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12904000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12613000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12202000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12718000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>12093000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>11964000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>11190000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>11968000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7930000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1602000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4474000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4765000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1063000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5500000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4891000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4609000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7926000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5190000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5431000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5406000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2591000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1296000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5377000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6534000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6021000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1693000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3634000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2922000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5173000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7340000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4354000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4357000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3381000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3190000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1389000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1611000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1981000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1335000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>988000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>720000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>367000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>384000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>632000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>61248000</v>
+      </c>
+      <c r="E59" s="3">
         <v>72293000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>57974000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>58232000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>59067000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>66102000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>56088000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>55448000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>54636000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>74662000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>74394000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>69818000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>70322000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>71435000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>70243000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>70240000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>71461000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>72659000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>74194000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>75860000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>74366000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>74419000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>72391000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>72565000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>65541000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>65484000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>64365000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>63210000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>60938000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>101620000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>40703000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>40096000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>37450000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>38560000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>35889000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>103654000</v>
+      </c>
+      <c r="E60" s="3">
         <v>97078000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>97300000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>96630000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>93258000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>95827000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>93062000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>92076000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>93510000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>90052000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>89618000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>84799000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>81692000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>81992000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>85771000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>88224000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>89892000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>87280000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>92307000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>92482000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>94502000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>97312000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>91846000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>92189000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>83615000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>81590000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>79417000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>77725000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>75532000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>74648000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>54409000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>52909000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>49781000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>50134000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>48489000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>47948000</v>
+      </c>
+      <c r="E61" s="3">
         <v>54356000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>53176000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>53162000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>46877000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>48621000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>47381000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>47659000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>47465000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51811000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>51788000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>51794000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>55150000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>56806000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>57042000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>57025000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>57554000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>61890000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>57325000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>58457000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>33754000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>19962000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>20298000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14859000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>11363000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10657000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10487000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10507000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10471000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9782000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9780000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10055000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10432000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9568000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>9824000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="3">
         <v>548000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2314000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2212000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2546000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>814000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2239000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2158000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2198000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11085000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13787000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13677000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14227000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14600000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18299000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20171000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20430000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>21041000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>23182000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>23315000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>24179000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>24651000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>24263000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>24156000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>24999000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>24702000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>25964000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>26337000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>26248000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>26219000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>25673000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>29050000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>29305000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>29418000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>28487000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6090,8 +6238,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6197,8 +6348,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6304,115 +6458,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>159819000</v>
+      </c>
+      <c r="E66" s="3">
         <v>160277000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>161257000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>160702000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>151500000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>154240000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>150998000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>150267000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>151831000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>152983000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>155257000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>150367000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>151199000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>153551000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>161286000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>165617000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>168093000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>170452000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>173082000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>174539000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>152740000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>142242000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>136714000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>131583000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>120084000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>117020000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>115948000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>114636000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>112327000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>110706000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>89921000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>92073000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>89578000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>89180000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>86861000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6450,8 +6610,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6557,8 +6718,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6664,8 +6828,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6673,7 +6840,7 @@
         <v>6000</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="F70" s="3">
         <v>0</v>
@@ -6771,8 +6938,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6878,115 +7048,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15239000</v>
+      </c>
+      <c r="E72" s="3">
         <v>15362000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19299000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>25469000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>26908000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>27251000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>27274000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>28910000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>29059000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>29473000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>30107000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>33382000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>33189000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>34408000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>38551000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>38660000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>38073000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>38610000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>47029000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>47478000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>49854000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>50644000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>53986000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>52819000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>58090000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>55941000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>54666000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>52303000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>52095000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>49618000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>44052000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>42222000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>42165000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>40714000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>40641000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7092,8 +7268,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7199,8 +7378,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7306,115 +7488,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-3331000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-3914000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-23552000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-17976000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-17009000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-17233000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-16729000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-15517000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-15508000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-15883000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-17699000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-14888000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-15398000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-14999000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-14440000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-16682000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-18058000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-18316000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-11821000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-11667000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-9665000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-8617000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-4116000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-5322000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>125000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>339000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-1289000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-1441000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1222000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1656000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1086000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-2037000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>95000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>817000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2089000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7520,227 +7708,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3865000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6170000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1439000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-343000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-23000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1636000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-149000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-414000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-629000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3275000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>193000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1219000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4143000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-109000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>587000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-537000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8420000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-449000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2376000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-628000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1010000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1166000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2147000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3422000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2361000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2196000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2474000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3318000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1808000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1749000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1577000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7778,115 +7975,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>442000</v>
+      </c>
+      <c r="E83" s="3">
         <v>246000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>467000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>456000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>457000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>261000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>493000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>498000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>486000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>502000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>493000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>498000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>486000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>534000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>523000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>551000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>536000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>578000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>565000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>547000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>556000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>628000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>576000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>546000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>521000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>583000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>523000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>507000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>501000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>582000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>522000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>494000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>471000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>546000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>474000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7992,8 +8193,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8099,8 +8303,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8206,8 +8413,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8313,8 +8523,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8420,115 +8633,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1616000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3450000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1345000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3923000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3362000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3381000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>22000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2875000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-318000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3457000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3190000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>81000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3216000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>716000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-262000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-483000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3387000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4009000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4819000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-5280000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4302000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2220000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2424000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-590000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2788000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2947000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4559000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4680000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3136000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2903000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3396000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4949000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2098000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2832000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3202000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8566,115 +8785,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-674000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-648000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-611000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-404000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-567000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-431000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-332000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-296000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-468000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-326000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-284000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-263000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-349000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-222000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-245000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-222000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-291000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-265000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-262000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-348000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-428000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-447000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-465000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-421000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-501000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-495000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-457000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-376000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-394000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-435000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-399000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-439000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-932000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-599000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-595000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8780,8 +9003,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8887,115 +9113,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1717000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12626000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>679000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2100000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2074000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2804000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-403000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3015000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1823000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2151000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>290000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>3266000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2965000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1935000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2966000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1659000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2764000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1543000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4137000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-12307000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-379000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>517000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1194000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-86000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-767000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2424000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-902000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1414000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>119000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-457000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-218000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1123000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-260000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1416000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-614000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9033,8 +9265,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9062,8 +9295,8 @@
       <c r="K96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9096,52 +9329,55 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-1158000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1157000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-1156000</v>
       </c>
       <c r="Z96" s="3">
         <v>-1156000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-1156000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1161000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-970000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-979000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-991000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-842000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-855000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-852000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-868000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-672000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-676000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9247,8 +9483,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9354,8 +9593,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9461,325 +9703,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-338000</v>
+      </c>
+      <c r="E100" s="3">
         <v>19971000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-300000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10000000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4462000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-356000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-38000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3413000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1680000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-250000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-18000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-602000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-396000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4362000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1171000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-19000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-48000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2681000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-468000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>22462000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>10280000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1403000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>4240000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2919000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2823000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-856000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3689000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4332000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2845000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2241000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3335000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3311000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2463000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1574000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2204000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E101" s="3">
         <v>52000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-24000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>10000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>61000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-63000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-68000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>61000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-63000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-68000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-20000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-18000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>59000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>37000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>36000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-47000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>22000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-25000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-44000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>8000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>7000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>21000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>32000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-27000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3659000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3840000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-933000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3980000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5778000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5881000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-443000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3811000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1117000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3399000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2677000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-650000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1716000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1513000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1161000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-689000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2812000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9387000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4911000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5552000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-278000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>597000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2240000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-801000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-349000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-33000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1110000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>418000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>212000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>547000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-605000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-185000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>381000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>BA</t>
   </si>
@@ -656,471 +656,483 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22749000</v>
+      </c>
+      <c r="E8" s="3">
         <v>19496000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15242000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17840000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16866000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16569000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>22018000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18104000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19751000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17921000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19980000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15956000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16681000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13991000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14793000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15278000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16998000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15217000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>15802000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14139000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11807000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16908000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>20560000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>19980000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>21361000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>22917000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>28341000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>25146000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>24258000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>23382000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>24770000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>24223000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>23051000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>21961000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>23286000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>23898000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20314000</v>
+      </c>
+      <c r="E9" s="3">
         <v>17049000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16784000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>21347000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15637000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14613000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>19173000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16939000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17812000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15493000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18124000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16778000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14559000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13645000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17307000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13566000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14588000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13808000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>20992000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13105000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12978000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>16768000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>18708000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16930000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>17810000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>18645000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>22090000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>21040000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>19536000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>18824000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>19881000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>19956000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>18702000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>18073000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>19464000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>19904000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2435000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2447000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-1542000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-3507000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1229000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1956000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2845000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1165000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1939000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2428000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1856000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-822000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2122000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>346000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-2514000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1712000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2410000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1409000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-5190000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1034000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-1171000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>140000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1852000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3050000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3551000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4272000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>6251000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4106000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4722000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4558000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4889000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4267000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4349000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3888000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3822000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3994000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1159,118 +1171,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>910000</v>
+      </c>
+      <c r="E12" s="3">
         <v>844000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>836000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1154000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>954000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>868000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>881000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>958000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>797000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>741000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>794000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>727000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>698000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>633000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>678000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>575000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>497000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>499000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>605000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>574000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>625000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>672000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>749000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>778000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>826000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>866000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>852000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>826000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>827000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>764000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>762000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>768000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>813000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>836000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>726000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>857000</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1379,46 +1395,49 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="E14" s="3">
         <v>33000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>15000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-5000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>80000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>147000</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>532000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>24</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>24</v>
@@ -1435,11 +1454,11 @@
       <c r="T14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V14" s="3">
         <v>498000</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>24</v>
@@ -1447,17 +1466,17 @@
       <c r="X14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z14" s="3">
         <v>2649000</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>5610000</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>24</v>
@@ -1468,8 +1487,8 @@
       <c r="AE14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1489,41 +1508,44 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>460000</v>
+      </c>
+      <c r="E15" s="3">
         <v>466000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>509000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>444000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>441000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>442000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>481000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>467000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>456000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>457000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1599,8 +1621,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1636,228 +1661,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>22971000</v>
+      </c>
+      <c r="E17" s="3">
         <v>18957000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18892000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23445000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17827000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16501000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>21448000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18791000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19747000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17389000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20325000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18748000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15901000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15153000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18964000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14949000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15975000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15300000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>23851000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14540000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>14771000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18261000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>22764000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>18721000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>24741000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>20567000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>24166000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>22919000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21548000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>20507000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>21792000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>21593000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>20521000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>19755000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>21103000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>21616000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-222000</v>
+      </c>
+      <c r="E18" s="3">
         <v>539000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3650000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5605000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-961000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>68000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>570000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-687000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>532000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-345000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2792000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>780000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1162000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4171000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>329000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1023000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-83000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8049000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-401000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2964000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1353000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2204000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1259000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3380000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2350000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4175000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2227000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2710000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2875000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2978000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2630000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2530000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2206000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2183000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2282000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1896,558 +1928,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-279000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-275000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-306000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-124000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-107000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-136000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-167000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-148000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-172000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-153000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>336000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>288000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>253000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>181000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>132000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>30000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>199000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>190000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>122000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>119000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>94000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>112000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>104000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>121000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>107000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>106000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>29000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>12000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>66000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>32000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>40000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>25000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>26000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>517000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1280000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2835000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5037000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-413000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>646000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1218000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-72000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>632000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1142000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>493000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2011000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1531000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-495000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3505000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>882000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1773000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>643000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7349000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>283000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2323000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-685000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1472000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1956000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2727000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2977000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4787000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2762000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3202000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3442000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3587000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3184000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3043000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2700000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2728000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>2758000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>710000</v>
+      </c>
+      <c r="E22" s="3">
         <v>708000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>755000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>728000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>673000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>569000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>600000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>589000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>621000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>649000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>640000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>628000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>656000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>637000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>661000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>669000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>673000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>679000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>698000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>643000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>553000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>262000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>242000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>203000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>154000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>123000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>158000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>106000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>109000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>102000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>93000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>87000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>93000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>87000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>79000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-561000</v>
+      </c>
+      <c r="E23" s="3">
         <v>76000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4093000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6224000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1515000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-378000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1100000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-400000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-496000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-649000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3132000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>377000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1618000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4700000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-310000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>549000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-572000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8625000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-925000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3423000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1503000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2342000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1177000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3427000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2333000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4046000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2133000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2586000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2839000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2917000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2583000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2462000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2145000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2103000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2203000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E24" s="3">
         <v>107000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-232000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-50000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-76000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-23000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>538000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-251000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-71000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>176000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>217000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-376000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-539000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-178000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-18000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-11000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-186000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-459000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1028000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-862000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1332000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>10000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-485000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>184000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>622000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-230000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>390000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>362000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>868000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>773000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>713000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>566000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>472000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2556,228 +2604,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-612000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-31000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3861000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6174000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1439000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-355000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-30000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1638000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-149000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-425000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-663000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3308000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>160000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1242000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4161000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-132000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>567000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-561000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8439000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-466000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2395000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-641000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1010000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1167000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2149000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3424000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2363000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2196000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2477000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2049000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1810000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1749000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1579000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1631000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2279000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-697000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-123000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3923000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6170000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1439000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-343000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-23000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1636000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-149000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-414000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-634000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3275000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>193000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1219000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4140000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-109000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>587000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-537000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8420000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-449000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2376000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-628000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1010000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1166000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2147000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3422000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2361000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2196000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2474000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2047000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1808000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1749000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1577000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1631000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2886,8 +2943,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2919,10 +2979,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>5000</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>24</v>
@@ -2930,17 +2990,17 @@
       <c r="P29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R29" s="3">
         <v>-3000</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2960,8 +3020,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
@@ -2978,11 +3038,11 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3">
         <v>1271000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>24</v>
@@ -2996,8 +3056,11 @@
       <c r="AL29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3106,8 +3169,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3216,228 +3282,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>279000</v>
+      </c>
+      <c r="E32" s="3">
         <v>275000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>306000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>124000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>107000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>136000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>167000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>148000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>172000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>153000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-336000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-288000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-253000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-181000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-132000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-30000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-199000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-190000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-122000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-119000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-94000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-112000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-104000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-121000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-107000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-106000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>15000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-66000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-32000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-611000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-37000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3865000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6170000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1439000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-343000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-23000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1636000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-149000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-414000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-629000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3275000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>193000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1219000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4143000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-109000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>587000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-537000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8420000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-449000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2376000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-628000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1010000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1166000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2147000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3422000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2361000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2196000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2474000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3318000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1808000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1749000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1577000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3546,233 +3621,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-611000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-37000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3865000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6170000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1439000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-343000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-23000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1636000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-149000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-414000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-629000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3275000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>193000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1219000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4143000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-109000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>587000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-537000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8420000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-449000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2376000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-628000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1010000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1166000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2147000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3422000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2361000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2196000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2474000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3318000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1808000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1749000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1577000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3811,8 +3895,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3851,543 +3936,556 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7087000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10142000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13801000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9961000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10894000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6914000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12691000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6811000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7254000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10812000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14614000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13494000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10090000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7409000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8052000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9764000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8271000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7059000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7752000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10564000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>19992000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>15039000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9485000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9763000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9167000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6836000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7637000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8034000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8121000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>9235000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8813000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8569000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8737000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8190000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>8801000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>8986000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>15171000</v>
+      </c>
+      <c r="E42" s="3">
         <v>13511000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>12460000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>488000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1706000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>594000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3252000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6540000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6487000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3931000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2606000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>763000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1358000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4873000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>8192000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>10231000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>13071000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>14861000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>17838000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>16552000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>12438000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>488000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>545000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1150000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>439000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>893000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>927000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1956000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1649000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>656000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1179000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1463000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1589000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1015000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1228000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>682000</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12451000</v>
+      </c>
+      <c r="E43" s="3">
         <v>12235000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11024000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12250000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12815000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12632000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10992000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12216000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12302000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12551000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11305000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12144000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12549000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11555000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11378000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12332000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11767000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11234000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>10051000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11722000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>11478000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>12725000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>12471000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>14808000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>13709000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>14217000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>14364000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>13260000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>12985000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>12868000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>11397000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>11079000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>10052000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>9915000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>9260000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>9889000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>87853000</v>
+      </c>
+      <c r="E44" s="3">
         <v>89077000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>87550000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>83341000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>85661000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>83471000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>79741000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>78972000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>78322000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>78503000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>78151000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>79777000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>79917000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>79819000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>78823000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>81897000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>81799000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>82668000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>81715000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>86961000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>83745000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>80020000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>76622000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>73279000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>68492000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>65369000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>62567000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>62038000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>61250000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>61303000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>33294000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>43031000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>42453000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>43247000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>43199000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>42680000</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4014000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2474000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2935000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2918000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3282000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2843000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2478000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2287000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2941000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2857000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2847000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3073000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2086000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2356000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2221000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2664000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4187000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4123000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4286000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5213000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2624000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2739000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3106000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2656000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3304000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2194000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2335000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2398000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2396000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2481000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2417000</v>
-      </c>
-      <c r="AH45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AI45" s="3" t="s">
         <v>24</v>
@@ -4401,448 +4499,463 @@
       <c r="AL45" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AM45" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>127301000</v>
+      </c>
+      <c r="E46" s="3">
         <v>127662000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>127998000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>109436000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>114439000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>106532000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>109275000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>106935000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>107412000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>108811000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>109523000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>109251000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>106000000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>106012000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>108666000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>116888000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>119095000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>119945000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>121642000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>131012000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>130277000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>111011000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>102229000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>101656000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>95111000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>89509000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>87830000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>87686000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>86401000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>86543000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>85194000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>64142000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>62831000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>62367000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>62488000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>62237000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1036000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1001000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>999000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1030000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1026000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1042000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1035000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1061000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1025000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>969000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2433000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2492000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2523000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2572000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2670000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2758000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2748000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2875000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2952000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3062000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3120000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3240000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3472000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3438000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3525000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3663000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3749000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4270000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4315000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4296000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4665000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5032000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5202000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5446000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>5060000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11658000</v>
+      </c>
+      <c r="E48" s="3">
         <v>11459000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13396000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11236000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10976000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10696000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12351000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10484000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10455000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10493000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10550000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10508000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10617000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10755000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10918000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11113000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11341000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11643000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13072000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11969000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12182000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12405000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13684000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13705000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13665000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13602000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12645000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12571000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12605000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12628000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12672000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12712000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12820000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12842000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12807000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>12713000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8822000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9995000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10041000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10123000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10175000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10123000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10187000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10212000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10255000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10317000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10368000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10416000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10486000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10557000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10630000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9785000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9915000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9930000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10195000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10341000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10466000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>11313000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11398000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11650000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11812000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11465000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>11269000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8252000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>8044000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8083000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8132000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>7867000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7914000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7838000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7864000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>7616000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4951,8 +5064,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5061,118 +5177,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5849000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5932000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3430000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5505000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5319000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5190000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3245000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4562000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4456000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4320000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4226000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4891000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5853000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5905000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5668000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6302000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5836000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5642000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4275000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4877000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6827000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5106000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2842000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2149000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2148000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1970000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1866000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1880000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1830000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1999000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1851000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1621000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1439000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1424000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1392000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5281,118 +5403,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>155120000</v>
+      </c>
+      <c r="E54" s="3">
         <v>156494000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>156363000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>137695000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>142720000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>134484000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>137012000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>134281000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>134774000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>136347000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>137100000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>137558000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>135479000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>135801000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>138552000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>146846000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>148935000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>150035000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>152136000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>161261000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>162872000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>143075000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>133625000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>132598000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>126261000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>120209000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>117359000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>114659000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>113195000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>113549000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>112362000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>91007000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>90036000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>89673000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>89997000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>88950000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5431,8 +5559,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5471,668 +5600,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11238000</v>
+      </c>
+      <c r="E57" s="3">
         <v>11034000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11364000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12267000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11864000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11616000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11964000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11143000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10936000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10274000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10200000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9793000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9575000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8779000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9261000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10151000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11450000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12410000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12928000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14479000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>13700000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>14963000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15553000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>15101000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>15267000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>14693000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12916000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>13663000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12904000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12613000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12202000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>12718000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>12093000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>11964000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>11190000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>11968000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8719000</v>
+      </c>
+      <c r="E58" s="3">
         <v>7930000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1602000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4474000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4765000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1063000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5500000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4891000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4609000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7926000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5190000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5431000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5406000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2591000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1296000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5377000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6534000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6021000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1693000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3634000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2922000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5173000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7340000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4354000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4357000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3381000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3190000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1389000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1611000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1981000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1335000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>988000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>720000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>367000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>384000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>632000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>59951000</v>
+      </c>
+      <c r="E59" s="3">
         <v>61248000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>72293000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>57974000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>58232000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>59067000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>66102000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>56088000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>55448000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>54636000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>74662000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>74394000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>69818000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>70322000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>71435000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>70243000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>70240000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>71461000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>72659000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>74194000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>75860000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>74366000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>74419000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>72391000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>72565000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>65541000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>65484000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>64365000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>63210000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>60938000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>101620000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>40703000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>40096000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>37450000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>38560000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>35889000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>103376000</v>
+      </c>
+      <c r="E60" s="3">
         <v>103654000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>97078000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>97300000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>96630000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>93258000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>95827000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>93062000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>92076000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>93510000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>90052000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>89618000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>84799000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>81692000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>81992000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>85771000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>88224000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>89892000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>87280000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>92307000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>92482000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>94502000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>97312000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>91846000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>92189000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>83615000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>81590000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>79417000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>77725000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>75532000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>74648000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>54409000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>52909000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>49781000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>50134000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>48489000</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>46928000</v>
+      </c>
+      <c r="E61" s="3">
         <v>47948000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>54356000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>53176000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>53162000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>46877000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>48621000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>47381000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>47659000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>47465000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>51811000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>51788000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>51794000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>55150000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>56806000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>57042000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>57025000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>57554000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>61890000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>57325000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>58457000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>33754000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>19962000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>20298000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14859000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11363000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10657000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10487000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10507000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10471000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9782000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9780000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10055000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>10432000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>9568000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>9824000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" s="3">
         <v>548000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2314000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2212000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2546000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>814000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2239000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2158000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2198000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11085000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13787000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13677000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14227000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14600000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18299000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20171000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>20430000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21041000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>23182000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>23315000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>24179000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>24651000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>24263000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>24156000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>24999000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>24702000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>25964000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>26337000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>26248000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>26219000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>25673000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>29050000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>29305000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>29418000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>28487000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6241,8 +6389,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6351,8 +6502,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6461,118 +6615,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>158416000</v>
+      </c>
+      <c r="E66" s="3">
         <v>159819000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>160277000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>161257000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>160702000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>151500000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>154240000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>150998000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>150267000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>151831000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>152983000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>155257000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>150367000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>151199000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>153551000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>161286000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>165617000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>168093000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>170452000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>173082000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>174539000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>152740000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>142242000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>136714000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>131583000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>120084000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>117020000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>115948000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>114636000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>112327000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>110706000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>89921000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>92073000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>89578000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>89180000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>86861000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6611,8 +6771,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6721,8 +6882,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6831,8 +6995,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6843,7 +7010,7 @@
         <v>6000</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="G70" s="3">
         <v>0</v>
@@ -6941,8 +7108,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7051,118 +7221,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14542000</v>
+      </c>
+      <c r="E72" s="3">
         <v>15239000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15362000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19299000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25469000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>26908000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>27251000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>27274000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>28910000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>29059000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>29473000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>30107000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>33382000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>33189000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>34408000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>38551000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>38660000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>38073000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>38610000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>47029000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>47478000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>49854000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>50644000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>53986000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>52819000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>58090000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>55941000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>54666000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>52303000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>52095000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>49618000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>44052000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>42222000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>42165000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>40714000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>40641000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7271,8 +7447,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7381,8 +7560,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7491,118 +7673,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-3301000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-3331000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-3914000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-23552000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-17976000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-17009000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-17233000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-16729000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-15517000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-15508000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-15883000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-17699000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-14888000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-15398000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-14999000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-14440000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-16682000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-18058000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-18316000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-11821000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-11667000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-9665000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-8617000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-4116000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-5322000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>125000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>339000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-1289000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-1441000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1222000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1656000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1086000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-2037000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>95000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>817000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>2089000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7711,233 +7899,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-611000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-37000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3865000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6170000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1439000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-343000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-23000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1636000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-149000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-414000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-629000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3275000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>193000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1219000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4143000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-109000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>587000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-537000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8420000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-449000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2376000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-628000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1010000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1166000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2147000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3422000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2361000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2196000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2474000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3318000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1808000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1749000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1577000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7976,118 +8173,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>441000</v>
+      </c>
+      <c r="E83" s="3">
         <v>442000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>246000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>467000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>456000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>457000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>261000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>493000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>498000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>486000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>502000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>493000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>498000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>486000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>534000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>523000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>551000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>536000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>578000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>565000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>547000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>556000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>628000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>576000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>546000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>521000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>583000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>523000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>507000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>501000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>582000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>522000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>494000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>471000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>546000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>474000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8196,8 +8397,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8306,8 +8510,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8416,8 +8623,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8526,8 +8736,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8636,118 +8849,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>227000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1616000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3450000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1345000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3923000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3362000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3381000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>22000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2875000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-318000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3457000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3190000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>81000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3216000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>716000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-262000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-483000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3387000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4009000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4819000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5280000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4302000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2220000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2424000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-590000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2788000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2947000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4559000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4680000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3136000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2903000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3396000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4949000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2098000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2832000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3202000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8786,118 +9005,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-427000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-674000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-648000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-611000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-404000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-567000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-431000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-332000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-296000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-468000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-326000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-284000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-263000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-349000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-222000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-245000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-222000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-291000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-265000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-262000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-348000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-428000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-447000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-465000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-421000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-501000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-495000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-457000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-376000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-394000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-435000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-399000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-439000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-932000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-599000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-595000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9006,8 +9229,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9116,118 +9342,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2229000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12626000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>679000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2100000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2074000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2804000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-403000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3015000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1823000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2151000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>290000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3266000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2965000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1935000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2966000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1659000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>2764000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1543000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4137000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-12307000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-379000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>517000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1194000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-86000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-767000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2424000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-902000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1414000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>119000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-457000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-218000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1123000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-260000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1416000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-614000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9266,8 +9498,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9298,8 +9531,8 @@
       <c r="L96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9332,52 +9565,55 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-1158000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1157000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-1156000</v>
       </c>
       <c r="AA96" s="3">
         <v>-1156000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-1156000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-1161000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-970000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-979000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-991000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-842000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-855000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-852000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-868000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-672000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-676000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9486,8 +9722,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9596,8 +9835,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9706,334 +9948,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-387000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-338000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>19971000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-300000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>10000000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4462000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-356000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-38000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3413000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1680000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-250000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-18000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-602000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-396000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4362000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1171000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-19000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-48000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2681000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-468000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>22462000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>10280000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1403000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4240000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2919000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2823000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-856000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3689000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4332000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2845000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2241000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3335000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-3311000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2463000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1574000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2204000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-28000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>52000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-24000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>10000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>61000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-63000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-68000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>61000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-63000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-68000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-20000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-18000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>59000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>37000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>36000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-47000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>22000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-25000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-44000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>8000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>7000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>21000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>32000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>20000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-27000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2367000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3659000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3840000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-933000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3980000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5778000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5881000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-443000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3811000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1117000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3399000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2677000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-650000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1716000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1513000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1161000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-689000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2812000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9387000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4911000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5552000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-278000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>597000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2240000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-801000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-349000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-33000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1110000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>418000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>212000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>547000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-605000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-185000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>381000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
   <si>
     <t>BA</t>
   </si>
@@ -656,495 +656,507 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>23948000</v>
+      </c>
+      <c r="E8" s="3">
         <v>23270000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22749000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19496000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15242000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>17840000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16866000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16569000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22018000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18104000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19751000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17921000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19980000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15956000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16681000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13991000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14793000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15278000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16998000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>15217000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>15802000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14139000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11807000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16908000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>20560000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>19980000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>21361000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>22917000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>28341000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>25146000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>24258000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>23382000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>24770000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>24223000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>23051000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>21961000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>23286000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>23898000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>22136000</v>
+      </c>
+      <c r="E9" s="3">
         <v>25645000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20314000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17049000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16784000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>21347000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15637000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14613000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19173000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16939000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>17812000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15493000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18124000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16778000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14559000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13645000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>17307000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13566000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14588000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13808000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>20992000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>13105000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12978000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16768000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>18708000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>16930000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>17810000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>18645000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>22090000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>21040000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>19536000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>18824000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>19881000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>19956000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>18702000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>18073000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>19464000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>19904000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1812000</v>
+      </c>
+      <c r="E10" s="3">
         <v>-2375000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2435000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2447000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-1542000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-3507000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1229000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1956000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2845000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1165000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1939000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2428000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1856000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-822000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2122000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>346000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-2514000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1712000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2410000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1409000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-5190000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1034000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-1171000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>140000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1852000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3050000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3551000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4272000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>6251000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4106000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4722000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4558000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4889000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4267000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>4349000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3888000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3822000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3994000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1185,124 +1197,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>964000</v>
+      </c>
+      <c r="E12" s="3">
         <v>897000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>910000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>844000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>836000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1154000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>954000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>868000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>881000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>958000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>797000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>741000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>794000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>727000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>698000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>633000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>678000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>575000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>497000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>499000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>605000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>574000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>625000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>672000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>749000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>778000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>826000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>866000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>852000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>826000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>827000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>764000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>762000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>768000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>813000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>836000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>726000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>857000</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1417,52 +1433,55 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-9609000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-67000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>33000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>15000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-5000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>80000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>147000</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-1000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>532000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>24</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>24</v>
@@ -1479,11 +1498,11 @@
       <c r="V14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X14" s="3">
         <v>498000</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>24</v>
@@ -1491,17 +1510,17 @@
       <c r="Z14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB14" s="3">
         <v>2649000</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>5610000</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>24</v>
@@ -1512,8 +1531,8 @@
       <c r="AG14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1533,47 +1552,50 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>536000</v>
+      </c>
+      <c r="E15" s="3">
         <v>491000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>460000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>466000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>509000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>444000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>441000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>442000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>481000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>467000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>456000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>457000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1649,8 +1671,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1688,240 +1713,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>24709000</v>
+      </c>
+      <c r="E17" s="3">
         <v>28017000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22971000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18957000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18892000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23445000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17827000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16501000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21448000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18791000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19747000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17389000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20325000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18748000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15901000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15153000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18964000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14949000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15975000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15300000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>23851000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14540000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14771000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>18261000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22764000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>18721000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>24741000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>20567000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>24166000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>22919000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>21548000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>20507000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>21792000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>21593000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>20521000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>19755000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>21103000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>21616000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-761000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4747000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-222000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>539000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3650000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5605000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-961000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>68000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>570000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-687000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>532000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-345000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2792000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>780000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1162000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4171000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>329000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1023000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-83000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8049000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-401000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2964000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1353000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2204000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1259000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3380000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2350000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4175000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2227000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2710000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2875000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2978000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2630000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2530000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2206000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2183000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2282000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1962,588 +1994,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-147000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-229000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-279000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-275000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-306000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-124000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-107000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-136000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-167000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-148000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-172000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-153000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>336000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>288000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>253000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>181000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>132000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>30000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>199000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>190000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>122000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>119000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>94000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>112000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>104000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>121000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>107000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>106000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>29000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>12000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>66000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>32000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>40000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>25000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>26000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4027000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>517000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1280000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2835000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5037000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-413000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>646000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1218000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-72000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>632000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1142000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>493000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2011000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1531000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-495000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3505000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>882000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1773000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>643000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-7349000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>283000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2323000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-685000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1472000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1956000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2727000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2977000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4787000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2762000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3202000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3442000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3587000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3184000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3043000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>2700000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2728000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2758000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>659000</v>
+      </c>
+      <c r="E22" s="3">
         <v>694000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>710000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>708000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>755000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>728000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>673000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>569000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>600000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>589000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>621000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>649000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>640000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>628000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>656000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>637000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>661000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>669000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>673000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>679000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>698000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>643000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>553000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>262000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>242000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>203000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>154000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>123000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>158000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>106000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>109000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>102000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>93000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>87000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>93000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>87000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>79000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>8319000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5199000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-561000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>76000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4093000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6224000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1515000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-378000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1100000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-400000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-496000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-649000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3132000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>377000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1618000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4700000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-310000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>549000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-572000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8625000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-925000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3423000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1503000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2342000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1177000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3427000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2333000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4046000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2133000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2586000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2839000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2917000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2583000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2462000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2145000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2103000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2203000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E24" s="3">
         <v>140000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>51000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>107000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-232000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-50000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-76000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-23000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>538000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-251000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-71000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>176000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>217000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-376000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-539000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-178000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-18000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-11000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-186000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-459000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1028000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-862000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1332000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>10000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-485000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>184000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>622000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-230000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>390000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>362000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>868000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>773000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>713000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>566000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>472000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2658,240 +2706,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>8220000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5339000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-612000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-31000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3861000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6174000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1439000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-355000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-30000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1638000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-149000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-425000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-663000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3308000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>160000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1242000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4161000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-132000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>567000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-561000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8439000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-466000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2395000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-641000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1010000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1167000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2149000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3424000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2363000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2196000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2477000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2049000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1810000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1749000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1579000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1631000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2279000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>8133000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5424000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-697000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-123000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3923000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6170000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1439000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-343000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-23000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1636000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-149000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-414000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-634000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3275000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>193000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1219000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4140000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-109000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>587000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-537000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8420000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-449000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2376000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-628000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1010000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1166000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2147000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3422000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2361000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2196000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2474000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2047000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1808000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1749000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1577000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1631000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3006,8 +3063,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3045,10 +3105,10 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>5000</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>24</v>
@@ -3056,17 +3116,17 @@
       <c r="R29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T29" s="3">
         <v>-3000</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -3086,8 +3146,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>24</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>24</v>
@@ -3104,11 +3164,11 @@
       <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>1271000</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>24</v>
@@ -3122,8 +3182,11 @@
       <c r="AN29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3238,8 +3301,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3354,240 +3420,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E32" s="3">
         <v>229000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>279000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>275000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>306000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>124000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>107000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>136000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>167000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>148000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>172000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>153000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-336000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-288000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-253000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-181000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-132000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-30000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-199000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-190000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-122000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-119000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-94000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-112000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-104000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-121000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-107000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-106000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>15000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-66000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-32000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8220000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5337000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-611000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-37000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3865000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6170000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1439000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-343000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-23000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1636000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-149000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-414000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-629000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3275000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>193000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1219000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4143000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-109000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>587000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-537000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8420000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-449000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2376000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-628000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1010000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1166000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2147000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3422000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2361000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2196000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2474000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3318000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1808000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1749000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1577000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3702,245 +3777,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8220000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5337000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-611000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-37000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3865000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6170000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1439000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-343000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-23000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1636000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-149000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-414000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-629000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3275000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>193000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1219000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4143000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-109000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>587000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-537000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8420000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-449000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2376000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-628000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1010000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1166000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2147000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3422000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2361000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2196000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2474000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3318000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1808000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1749000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1577000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3981,8 +4065,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4023,573 +4108,586 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10921000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6173000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7087000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10142000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13801000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9961000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10894000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6914000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12691000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6811000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7254000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10812000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14614000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13494000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10090000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7409000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8052000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9764000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8271000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7059000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7752000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10564000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>19992000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>15039000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9485000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9763000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>9167000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6836000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7637000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8034000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8121000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>9235000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8813000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8569000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>8737000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>8190000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>8801000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>8986000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>17737000</v>
+      </c>
+      <c r="E42" s="3">
         <v>16102000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>15171000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13511000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12460000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>488000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1706000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>594000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3252000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6540000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6487000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3931000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2606000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>763000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1358000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4873000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>8192000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>10231000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>13071000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>14861000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>17838000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>16552000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>12438000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>488000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>545000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1150000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>439000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>893000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>927000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1956000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1649000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>656000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1179000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1463000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1589000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1015000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1228000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>682000</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12105000</v>
+      </c>
+      <c r="E43" s="3">
         <v>12346000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12451000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12235000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11024000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12250000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12815000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12632000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10992000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12216000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12302000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12551000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11305000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12144000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12549000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11555000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11378000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12332000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11767000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11234000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>10051000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>11722000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>11478000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>12725000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>12471000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>14808000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>13709000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>14217000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>14364000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>13260000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>12985000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>12868000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>11397000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>11079000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>10052000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>9915000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>9260000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>9889000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>84679000</v>
+      </c>
+      <c r="E44" s="3">
         <v>82425000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>87853000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>89077000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>87550000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>83341000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>85661000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>83471000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>79741000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>78972000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>78322000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>78503000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>78151000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>79777000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>79917000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>79819000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>78823000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>81897000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>81799000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>82668000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>81715000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>86961000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>83745000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>80020000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>76622000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>73279000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>68492000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>65369000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>62567000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>62038000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>61250000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>61303000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>33294000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>43031000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>42453000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>43247000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>43199000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>42680000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2275000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4377000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4014000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2474000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2935000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2918000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3282000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2843000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2478000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2287000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2941000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2857000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2847000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3073000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2086000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2356000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2221000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2664000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4187000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4123000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4286000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5213000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2624000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2739000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3106000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2656000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3304000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2194000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2335000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2398000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2396000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2481000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2417000</v>
-      </c>
-      <c r="AJ45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AK45" s="3" t="s">
         <v>24</v>
@@ -4603,472 +4701,487 @@
       <c r="AN45" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AO45" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>128459000</v>
+      </c>
+      <c r="E46" s="3">
         <v>122132000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>127301000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>127662000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>127998000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>109436000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>114439000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>106532000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>109275000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>106935000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>107412000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>108811000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>109523000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>109251000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>106000000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>106012000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>108666000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>116888000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>119095000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>119945000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>121642000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>131012000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>130277000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>111011000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>102229000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>101656000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>95111000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>89509000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>87830000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>87686000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>86401000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>86543000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>85194000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>64142000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>62831000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>62367000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>62488000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>62237000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1048000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1050000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1036000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1001000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>999000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1030000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1026000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1042000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1035000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1061000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1025000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>969000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2433000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2492000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2523000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2572000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2670000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2758000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2748000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2875000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2952000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3062000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3120000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3240000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3472000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3438000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3525000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3663000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3749000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4270000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4315000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4296000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>4665000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5032000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>5202000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>5446000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>5060000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17484000</v>
+      </c>
+      <c r="E48" s="3">
         <v>12078000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11658000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11459000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13396000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11236000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10976000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10696000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12351000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10484000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10455000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10493000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10550000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10508000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10617000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10755000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10918000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11113000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11341000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11643000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13072000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11969000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12182000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12405000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13684000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13705000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13665000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13602000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12645000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12571000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12605000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12628000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12672000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12712000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12820000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>12842000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>12807000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>12713000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18842000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8776000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8822000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9995000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10041000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10123000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10175000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10123000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10187000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10212000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10255000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10317000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10368000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10416000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10486000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10557000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10630000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9785000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9915000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9930000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10195000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10341000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10466000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11313000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11398000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11650000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>11812000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>11465000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11269000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8252000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8044000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8083000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>8132000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7867000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7914000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>7838000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>7864000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>7616000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5183,8 +5296,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5299,124 +5415,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2054000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5698000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5849000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5932000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3430000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5505000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5319000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5190000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3245000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4562000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4456000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4320000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4226000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4891000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5853000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5905000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5668000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6302000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5836000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5642000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4275000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4877000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6827000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5106000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2842000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2149000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2148000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1970000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1866000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1880000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1830000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1999000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1851000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1621000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1439000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1424000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1392000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5531,124 +5653,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>168235000</v>
+      </c>
+      <c r="E54" s="3">
         <v>150023000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>155120000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>156494000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>156363000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>137695000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>142720000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>134484000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>137012000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>134281000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>134774000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>136347000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>137100000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>137558000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>135479000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>135801000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>138552000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>146846000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>148935000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>150035000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>152136000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>161261000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>162872000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>143075000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>133625000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>132598000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>126261000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>120209000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>117359000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>114659000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>113195000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>113549000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>112362000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>91007000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>90036000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>89673000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>89997000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>88950000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5689,8 +5817,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5731,593 +5860,609 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13109000</v>
+      </c>
+      <c r="E57" s="3">
         <v>11732000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11238000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11034000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11364000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12267000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11864000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11616000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11964000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11143000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10936000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10274000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10200000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9793000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9575000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8779000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9261000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10151000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11450000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12410000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12928000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>14479000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>13700000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>14963000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>15553000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>15101000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>15267000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>14693000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12916000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>13663000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12904000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>12613000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>12202000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>12718000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>12093000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>11964000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>11190000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>11968000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8796000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8742000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8719000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7930000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1602000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4474000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4765000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1063000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5500000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4891000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4609000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7926000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5190000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5431000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5406000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2591000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1296000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5377000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6534000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6021000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1693000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3634000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2922000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5173000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7340000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4354000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4357000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3381000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3190000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1389000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1611000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1981000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1335000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>988000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>720000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>367000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>384000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>632000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>72056000</v>
+      </c>
+      <c r="E59" s="3">
         <v>58540000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>59951000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>61248000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>72293000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>57974000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>58232000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>59067000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>66102000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>56088000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>55448000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>54636000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>74662000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>74394000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>69818000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>70322000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>71435000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>70243000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>70240000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>71461000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>72659000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>74194000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>75860000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>74366000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>74419000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>72391000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>72565000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>65541000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>65484000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>64365000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>63210000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>60938000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>101620000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>40703000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>40096000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>37450000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>38560000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>35889000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>108115000</v>
+      </c>
+      <c r="E60" s="3">
         <v>103324000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>103376000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>103654000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>97078000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>97300000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>96630000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>93258000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>95827000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>93062000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>92076000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>93510000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>90052000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>89618000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>84799000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>81692000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>81992000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>85771000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>88224000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>89892000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>87280000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>92307000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>92482000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>94502000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>97312000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>91846000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>92189000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>83615000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>81590000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>79417000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>77725000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>75532000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>74648000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>54409000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>52909000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>49781000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>50134000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>48489000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>47569000</v>
+      </c>
+      <c r="E61" s="3">
         <v>46961000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>46928000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>47948000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>54356000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>53176000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>53162000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>46877000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>48621000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>47381000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>47659000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>47465000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>51811000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>51788000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>51794000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>55150000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>56806000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>57042000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>57025000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>57554000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>61890000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>57325000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>58457000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>33754000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>19962000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>20298000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14859000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11363000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10657000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10487000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10507000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10471000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>9782000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9780000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>10055000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>10432000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>9568000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>9824000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>24</v>
+      <c r="D62" s="3">
+        <v>500000</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>24</v>
@@ -6325,110 +6470,113 @@
       <c r="F62" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H62" s="3">
         <v>548000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2314000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2212000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2546000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>814000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2239000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2158000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2198000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11085000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13787000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13677000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14227000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14600000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18299000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>20171000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>20430000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>21041000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>23182000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>23315000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>24179000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>24651000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>24263000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>24156000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>24999000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>24702000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>25964000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>26337000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>26248000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>26219000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>25673000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>29050000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>29305000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>29418000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>28487000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6543,8 +6691,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6659,8 +6810,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6775,124 +6929,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>162778000</v>
+      </c>
+      <c r="E66" s="3">
         <v>158276000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>158416000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>159819000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>160277000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>161257000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>160702000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>151500000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>154240000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>150998000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>150267000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>151831000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>152983000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>155257000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>150367000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>151199000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>153551000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>161286000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>165617000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>168093000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>170452000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>173082000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>174539000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>152740000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>142242000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>136714000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>131583000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>120084000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>117020000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>115948000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>114636000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>112327000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>110706000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>89921000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>92073000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>89578000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>89180000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>86861000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6933,8 +7093,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7049,8 +7210,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7165,8 +7329,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7183,7 +7350,7 @@
         <v>6000</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -7281,8 +7448,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7397,124 +7567,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17252000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9118000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>14542000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15239000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15362000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19299000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25469000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>26908000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27251000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27274000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>28910000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>29059000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>29473000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>30107000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>33382000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>33189000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>34408000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>38551000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>38660000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>38073000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>38610000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>47029000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>47478000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>49854000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>50644000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>53986000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>52819000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>58090000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>55941000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>54666000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>52303000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>52095000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>49618000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>44052000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>42222000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>42165000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>40714000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>40641000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7629,8 +7805,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7745,8 +7924,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7861,124 +8043,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5448000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-8256000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-3301000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-3331000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-3914000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-23552000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-17976000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-17009000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-17233000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-16729000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-15517000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-15508000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-15883000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-17699000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-14888000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-15398000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-14999000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-14440000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-16682000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-18058000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-18316000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-11821000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-11667000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-9665000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-8617000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-4116000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-5322000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>125000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>339000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-1289000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-1441000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1222000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1656000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1086000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>-2037000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>95000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>817000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>2089000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8093,245 +8281,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8220000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5337000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-611000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-37000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3865000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6170000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1439000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-343000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-23000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1636000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-149000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-414000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-629000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3275000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>193000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1219000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4143000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-109000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>587000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-537000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8420000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-449000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2376000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-628000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1010000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1166000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2147000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3422000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2361000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2196000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2474000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3318000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1808000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1749000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1577000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8372,124 +8569,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>286000</v>
+      </c>
+      <c r="E83" s="3">
         <v>444000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>441000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>442000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>246000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>467000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>456000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>457000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>261000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>493000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>498000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>486000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>502000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>493000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>498000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>486000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>534000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>523000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>551000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>536000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>578000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>565000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>547000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>556000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>628000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>576000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>546000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>521000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>583000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>523000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>507000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>501000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>582000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>522000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>494000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>471000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>546000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>474000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8604,8 +8805,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8720,8 +8924,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8836,8 +9043,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8952,8 +9162,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9068,124 +9281,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1331000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1123000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>227000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1616000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3450000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1345000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3923000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3362000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3381000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>22000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2875000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-318000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3457000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3190000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>81000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3216000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>716000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-262000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-483000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3387000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4009000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4819000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-5280000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4302000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2220000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2424000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-590000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2788000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2947000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4559000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4680000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3136000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2903000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3396000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>4949000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>2098000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>2832000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>3202000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9226,124 +9445,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-956000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-885000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-427000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-674000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-648000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-611000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-404000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-567000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-431000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-332000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-296000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-468000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-326000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-284000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-263000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-349000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-222000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-245000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-222000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-291000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-265000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-262000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-348000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-428000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-447000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-465000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-421000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-501000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-495000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-457000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-376000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-394000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-435000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-399000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-439000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-932000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-599000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-595000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9458,8 +9681,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9574,124 +9800,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>6400000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1955000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2229000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12626000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>679000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2100000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2074000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2804000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-403000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3015000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1823000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2151000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>290000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>3266000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2965000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1935000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>2966000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1659000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>2764000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1543000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4137000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-12307000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-379000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>517000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1194000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-86000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-767000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2424000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-902000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1414000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>119000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-457000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-218000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1123000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-260000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1416000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-614000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9732,8 +9964,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9770,8 +10003,8 @@
       <c r="N96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9804,52 +10037,55 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-1158000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1157000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-1156000</v>
       </c>
       <c r="AC96" s="3">
         <v>-1156000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-1156000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-1161000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-970000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-979000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-991000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-842000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-855000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-852000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-868000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-672000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-676000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9964,8 +10200,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10080,8 +10319,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10196,352 +10438,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2951000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-87000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-387000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-338000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>19971000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-300000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>10000000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4462000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-356000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-38000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3413000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1680000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-250000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-602000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-396000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4362000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1171000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-19000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-48000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2681000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-468000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>22462000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>10280000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1403000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4240000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2919000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2823000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-856000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3689000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4332000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2845000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2241000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-3335000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-3311000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2463000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1574000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-2204000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="E101" s="3">
         <v>33000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-28000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>52000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-24000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>10000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>61000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-63000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-68000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>61000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-63000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-68000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-5000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-20000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>4000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-18000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>59000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>37000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>36000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-47000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>22000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-25000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-44000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>8000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>21000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>32000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>20000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-27000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4781000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-914000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2367000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3659000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3840000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-933000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3980000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5778000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5881000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-443000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3811000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1117000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3399000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2677000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-650000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1716000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1513000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1161000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-689000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2812000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-9387000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4911000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5552000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-278000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>597000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2240000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-801000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-349000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-33000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1110000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>418000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>212000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>547000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-605000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-185000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>381000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>BA</t>
   </si>
@@ -656,507 +656,519 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22217000</v>
+      </c>
+      <c r="E8" s="3">
         <v>23948000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23270000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22749000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19496000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15242000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>17840000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16866000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16569000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>22018000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18104000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19751000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17921000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19980000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15956000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16681000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13991000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14793000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>15278000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16998000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>15217000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>15802000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14139000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11807000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16908000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>20560000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>19980000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>21361000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>22917000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>28341000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>25146000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>24258000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>23382000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>24770000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>24223000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>23051000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>21961000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>23286000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>23898000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>19671000</v>
+      </c>
+      <c r="E9" s="3">
         <v>22136000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25645000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20314000</v>
       </c>
-      <c r="G9" s="3">
-        <v>17049000</v>
-      </c>
       <c r="H9" s="3">
+        <v>17079000</v>
+      </c>
+      <c r="I9" s="3">
         <v>16784000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>21347000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15637000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14613000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>19173000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16939000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17812000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15493000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18124000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16778000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14559000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13645000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>17307000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13566000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14588000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13808000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>20992000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13105000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12978000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>16768000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>18708000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>16930000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>17810000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>18645000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>22090000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>21040000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>19536000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>18824000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>19881000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>19956000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>18702000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>18073000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>19464000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>19904000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2546000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1812000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-2375000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2435000</v>
       </c>
-      <c r="G10" s="3">
-        <v>2447000</v>
-      </c>
       <c r="H10" s="3">
+        <v>2417000</v>
+      </c>
+      <c r="I10" s="3">
         <v>-1542000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-3507000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1229000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1956000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2845000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1165000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1939000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2428000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1856000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-822000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2122000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>346000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-2514000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1712000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2410000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1409000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-5190000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1034000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>140000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1852000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3050000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3551000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4272000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>6251000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4106000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4722000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4558000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4889000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>4267000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>4349000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3888000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3822000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>3994000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1198,127 +1210,131 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>903000</v>
+      </c>
+      <c r="E12" s="3">
         <v>964000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>897000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>910000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>844000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>836000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1154000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>954000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>868000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>881000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>958000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>797000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>741000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>794000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>727000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>698000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>633000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>678000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>575000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>497000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>499000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>605000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>574000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>625000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>672000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>749000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>778000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>826000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>866000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>852000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>826000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>827000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>764000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>762000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>768000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>813000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>836000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>726000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>857000</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1436,55 +1452,58 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-9609000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-67000</v>
       </c>
-      <c r="G14" s="3">
-        <v>33000</v>
-      </c>
       <c r="H14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I14" s="3">
         <v>6000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>15000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-5000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>80000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>147000</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-1000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>532000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>24</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>24</v>
@@ -1501,11 +1520,11 @@
       <c r="W14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y14" s="3">
         <v>498000</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>24</v>
@@ -1513,17 +1532,17 @@
       <c r="AA14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC14" s="3">
         <v>2649000</v>
       </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AD14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5610000</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>24</v>
@@ -1534,8 +1553,8 @@
       <c r="AH14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
@@ -1555,50 +1574,53 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>573000</v>
+      </c>
+      <c r="E15" s="3">
         <v>536000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>491000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>460000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>466000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>509000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>444000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>441000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>442000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>481000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>467000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>456000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>457000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1674,8 +1696,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1714,246 +1739,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>21836000</v>
+      </c>
+      <c r="E17" s="3">
         <v>24709000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28017000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>22971000</v>
       </c>
-      <c r="G17" s="3">
-        <v>18957000</v>
-      </c>
       <c r="H17" s="3">
+        <v>18987000</v>
+      </c>
+      <c r="I17" s="3">
         <v>18892000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23445000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17827000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16501000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21448000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18791000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19747000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17389000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20325000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18748000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15901000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15153000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18964000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14949000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15975000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15300000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>23851000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14540000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>14771000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>18261000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>22764000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>18721000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>24741000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>20567000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>24166000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>22919000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>21548000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>20507000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>21792000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>21593000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>20521000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>19755000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>21103000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>21616000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>381000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-761000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4747000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-222000</v>
       </c>
-      <c r="G18" s="3">
-        <v>539000</v>
-      </c>
       <c r="H18" s="3">
+        <v>509000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-3650000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5605000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-961000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>68000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>570000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-687000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>532000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-345000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2792000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>780000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1162000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4171000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>329000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1023000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-83000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8049000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-401000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2964000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1353000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2204000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1259000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3380000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2350000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4175000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2227000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2710000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2875000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2978000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2630000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2530000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2206000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2183000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2282000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1995,603 +2027,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-259000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-147000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-229000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-279000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-275000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-306000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-124000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-107000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-136000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-167000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-148000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-172000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-153000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>336000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>288000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>253000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>181000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>132000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>30000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>199000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>190000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>122000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>119000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>94000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>112000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>104000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>121000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>107000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>106000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>29000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>12000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>66000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>32000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>40000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>25000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>26000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1213000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-78000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4027000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>517000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1280000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-2835000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5037000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-413000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>646000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1218000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-72000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>632000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1142000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>493000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2011000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1531000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-495000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3505000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>882000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1773000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>643000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-7349000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>283000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2323000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-685000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1472000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1956000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-2727000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2977000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4787000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2762000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3202000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3442000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3587000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3184000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3043000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2700000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2728000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2758000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>616000</v>
+      </c>
+      <c r="E22" s="3">
         <v>659000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>694000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>710000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>708000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>755000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>728000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>673000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>569000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>600000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>589000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>621000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>649000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>640000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>628000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>656000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>637000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>661000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>669000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>673000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>679000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>698000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>643000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>553000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>262000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>242000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>203000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>154000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>123000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>158000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>106000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>109000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>102000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>93000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>87000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>93000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>87000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>79000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E23" s="3">
         <v>8319000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5199000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-561000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>76000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4093000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6224000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1515000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-378000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1100000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-400000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-496000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-649000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3132000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>377000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1618000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4700000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-310000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>549000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-572000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8625000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-925000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3423000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1503000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2342000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1177000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3427000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2333000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4046000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2133000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2586000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2839000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2917000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2583000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2462000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2145000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2103000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2203000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E24" s="3">
         <v>99000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>140000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>51000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>107000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-232000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-50000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-76000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-23000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>21000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>538000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-251000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-71000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>176000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>217000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-376000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-539000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-178000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-18000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-11000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-186000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-459000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1028000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-862000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1332000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>10000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-485000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>184000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>622000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-230000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>390000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>362000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>868000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>773000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>713000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>566000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>472000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2709,246 +2757,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E26" s="3">
         <v>8220000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5339000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-612000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-31000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3861000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6174000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1439000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-355000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1638000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-149000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-425000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-663000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3308000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>160000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1242000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4161000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-132000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>567000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-561000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8439000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-466000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2395000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-641000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1010000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1167000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2149000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3424000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2363000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2196000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2477000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2049000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1810000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1749000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1579000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1631000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>2279000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="E27" s="3">
         <v>8133000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5424000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-697000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-123000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3923000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6170000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1439000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-343000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-23000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1636000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-149000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-414000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-634000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3275000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>193000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1219000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4140000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-109000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>587000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-537000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8420000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-449000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2376000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-628000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1010000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1166000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2147000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3422000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2361000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2196000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2474000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2047000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1808000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1749000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1577000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1631000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3066,8 +3123,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3108,10 +3168,10 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>5000</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>24</v>
@@ -3119,17 +3179,17 @@
       <c r="S29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U29" s="3">
         <v>-3000</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -3149,8 +3209,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -3167,11 +3227,11 @@
       <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK29" s="3">
         <v>1271000</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>24</v>
@@ -3185,8 +3245,11 @@
       <c r="AO29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3304,8 +3367,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3423,246 +3489,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E32" s="3">
         <v>147000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>229000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>279000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>275000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>306000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>124000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>107000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>136000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>167000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>148000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>172000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>153000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-336000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-288000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-253000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-181000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-132000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-30000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-199000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-190000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-122000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-119000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-94000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-112000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-104000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-121000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-107000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-106000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>15000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-66000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-32000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E33" s="3">
         <v>8220000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5337000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-611000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-37000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3865000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6170000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1439000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-343000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-23000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1636000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-149000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-414000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-629000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3275000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>193000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1219000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4143000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-109000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>587000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-537000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8420000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-449000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2376000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-628000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1010000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1166000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2147000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3422000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2361000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2196000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2474000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3318000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1808000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1749000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1577000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3780,251 +3855,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E35" s="3">
         <v>8220000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5337000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-611000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-37000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3865000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6170000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1439000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-343000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-23000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1636000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-149000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-414000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-629000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3275000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>193000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1219000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4143000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-109000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>587000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-537000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8420000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-449000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2376000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-628000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1010000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1166000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2147000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3422000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2361000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2196000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2474000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3318000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1808000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1749000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1577000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4066,8 +4150,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4109,588 +4194,601 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9441000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10921000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6173000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7087000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10142000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13801000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9961000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10894000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6914000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12691000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6811000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7254000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10812000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14614000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13494000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10090000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7409000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8052000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9764000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8271000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7059000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7752000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10564000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>19992000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>15039000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9485000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>9763000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>9167000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6836000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7637000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8034000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8121000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>9235000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8813000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>8569000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>8737000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>8190000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>8801000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>8986000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10737000</v>
+      </c>
+      <c r="E42" s="3">
         <v>17737000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>16102000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15171000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13511000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12460000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>488000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1706000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>594000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3252000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6540000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>6487000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3931000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2606000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>763000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1358000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4873000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>8192000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>10231000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>13071000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>14861000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>17838000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>16552000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>12438000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>488000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>545000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1150000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>439000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>893000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>927000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1956000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1649000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>656000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1179000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1463000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1589000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1015000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1228000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>682000</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13278000</v>
+      </c>
+      <c r="E43" s="3">
         <v>12105000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12346000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12451000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12235000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11024000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12250000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12815000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12632000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10992000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12216000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12302000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12551000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11305000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12144000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12549000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11555000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11378000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12332000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11767000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>11234000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>10051000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>11722000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>11478000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>12725000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>12471000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>14808000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>13709000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>14217000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>14364000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>13260000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>12985000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>12868000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>11397000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>11079000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>10052000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>9915000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>9260000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>9889000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>87225000</v>
+      </c>
+      <c r="E44" s="3">
         <v>84679000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>82425000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>87853000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>89077000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>87550000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>83341000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>85661000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>83471000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>79741000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>78972000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>78322000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>78503000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>78151000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>79777000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>79917000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>79819000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>78823000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>81897000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>81799000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>82668000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>81715000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>86961000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>83745000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>80020000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>76622000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>73279000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>68492000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>65369000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>62567000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>62038000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>61250000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>61303000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>33294000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>43031000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>42453000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>43247000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>43199000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>42680000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2733000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2275000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4377000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4014000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2474000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2935000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2918000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3282000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2843000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2478000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2287000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2941000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2857000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2847000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3073000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2086000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2356000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2221000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2664000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4187000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4123000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4286000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5213000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2624000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2739000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3106000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2656000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3304000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2194000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2335000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2398000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2396000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2481000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2417000</v>
-      </c>
-      <c r="AK45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AL45" s="3" t="s">
         <v>24</v>
@@ -4704,127 +4802,133 @@
       <c r="AO45" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AP45" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>124141000</v>
+      </c>
+      <c r="E46" s="3">
         <v>128459000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>122132000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>127301000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>127662000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>127998000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>109436000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>114439000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>106532000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>109275000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>106935000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>107412000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>108811000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>109523000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>109251000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>106000000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>106012000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>108666000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>116888000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>119095000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>119945000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>121642000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>131012000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>130277000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>111011000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>102229000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>101656000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>95111000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>89509000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>87830000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>87686000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>86401000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>86543000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>85194000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>64142000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>62831000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>62367000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>62488000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>62237000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4832,356 +4936,365 @@
         <v>1048000</v>
       </c>
       <c r="E47" s="3">
+        <v>1048000</v>
+      </c>
+      <c r="F47" s="3">
         <v>1050000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1036000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1001000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>999000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1030000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1026000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1042000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1035000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1061000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1025000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>969000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2433000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2492000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2523000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2572000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2670000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2758000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2748000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2875000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2952000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3062000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3120000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3240000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3472000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3438000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3525000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3663000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3749000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4270000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4315000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4296000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>4665000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>5032000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>5202000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>5446000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>5060000</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16152000</v>
+      </c>
+      <c r="E48" s="3">
         <v>17484000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12078000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11658000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11459000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13396000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11236000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10976000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10696000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12351000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10484000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10455000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10493000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10550000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10508000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10617000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10755000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10918000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11113000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11341000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11643000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13072000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11969000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12182000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12405000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13684000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13705000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13665000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13602000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12645000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12571000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12605000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12628000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12672000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12712000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>12820000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>12842000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>12807000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>12713000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19150000</v>
+      </c>
+      <c r="E49" s="3">
         <v>18842000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8776000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8822000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9995000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10041000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10123000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10175000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10123000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10187000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10212000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10255000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10317000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10368000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10416000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10486000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10557000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10630000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9785000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9915000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9930000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10195000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10341000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10466000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11313000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11398000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>11650000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>11812000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11465000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>11269000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8252000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8044000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>8083000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>8132000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7867000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>7914000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>7838000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>7864000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>7616000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5299,8 +5412,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5418,127 +5534,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4160000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2054000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5698000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5849000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5932000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3430000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5505000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5319000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5190000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3245000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4562000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4456000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4320000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4226000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4891000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5853000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5905000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5668000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6302000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5836000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5642000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4275000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4877000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6827000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5106000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2842000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2149000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2148000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1970000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1866000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1880000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1830000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1999000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1851000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1621000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1439000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1424000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1392000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5656,127 +5778,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>164787000</v>
+      </c>
+      <c r="E54" s="3">
         <v>168235000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>150023000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>155120000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>156494000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>156363000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>137695000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>142720000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>134484000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>137012000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>134281000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>134774000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>136347000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>137100000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>137558000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>135479000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>135801000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>138552000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>146846000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>148935000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>150035000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>152136000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>161261000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>162872000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>143075000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>133625000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>132598000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>126261000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>120209000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>117359000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>114659000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>113195000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>113549000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>112362000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>91007000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>90036000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>89673000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>89997000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>88950000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5818,8 +5946,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5861,611 +5990,627 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13713000</v>
+      </c>
+      <c r="E57" s="3">
         <v>13109000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11732000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11238000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11034000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11364000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12267000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11864000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11616000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11964000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11143000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10936000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10274000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10200000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9793000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9575000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8779000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9261000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10151000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11450000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12410000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12928000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>14479000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13700000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>14963000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>15553000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>15101000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>15267000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>14693000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12916000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>13663000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>12904000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>12613000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>12202000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>12718000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>12093000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>11964000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>11190000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>11968000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2855000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8796000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8742000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8719000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7930000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1602000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4474000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4765000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1063000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5500000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4891000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4609000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7926000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5190000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5431000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5406000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2591000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1296000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5377000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6534000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>6021000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1693000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3634000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2922000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5173000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7340000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4354000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4357000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3381000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3190000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1389000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1611000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1981000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1335000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>988000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>720000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>367000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>384000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>632000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>62651000</v>
+      </c>
+      <c r="E59" s="3">
         <v>72056000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>58540000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>59951000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>61248000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>72293000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>57974000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>58232000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>59067000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>66102000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>56088000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>55448000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>54636000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>74662000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>74394000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>69818000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>70322000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>71435000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>70243000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>70240000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>71461000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>72659000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>74194000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>75860000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>74366000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>74419000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>72391000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>72565000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>65541000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>65484000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>64365000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>63210000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>60938000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>101620000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>40703000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>40096000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>37450000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>38560000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>35889000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>105547000</v>
+      </c>
+      <c r="E60" s="3">
         <v>108115000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>103324000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>103376000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>103654000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>97078000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>97300000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>96630000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>93258000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>95827000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>93062000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>92076000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>93510000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>90052000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>89618000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>84799000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>81692000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>81992000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>85771000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>88224000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>89892000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>87280000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>92307000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>92482000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>94502000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>97312000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>91846000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>92189000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>83615000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>81590000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>79417000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>77725000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>75532000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>74648000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>54409000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>52909000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>49781000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>50134000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>48489000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>46759000</v>
+      </c>
+      <c r="E61" s="3">
         <v>47569000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>46961000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>46928000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>47948000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>54356000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>53176000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>53162000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>46877000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>48621000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>47381000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>47659000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>47465000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>51811000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>51788000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>51794000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>55150000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>56806000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>57042000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>57025000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>57554000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>61890000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>57325000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>58457000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>33754000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>19962000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>20298000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>14859000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11363000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10657000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10487000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10507000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10471000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9782000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>9780000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>10055000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>10432000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>9568000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>9824000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="3">
         <v>500000</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>24</v>
@@ -6473,110 +6618,113 @@
       <c r="G62" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62" s="3">
         <v>548000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2314000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2212000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2546000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>814000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2239000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2158000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2198000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11085000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13787000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13677000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14227000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>14600000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>18299000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>20171000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>20430000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>21041000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>23182000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>23315000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>24179000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>24651000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>24263000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>24156000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>24999000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>24702000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>25964000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>26337000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>26248000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>26219000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>25673000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>29050000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>29305000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>29418000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>28487000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6694,8 +6842,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6813,8 +6964,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6932,127 +7086,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>158800000</v>
+      </c>
+      <c r="E66" s="3">
         <v>162778000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>158276000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>158416000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>159819000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>160277000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>161257000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>160702000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>151500000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>154240000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>150998000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>150267000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>151831000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>152983000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>155257000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>150367000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>151199000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>153551000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>161286000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>165617000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>168093000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>170452000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>173082000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>174539000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>152740000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>142242000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>136714000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>131583000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>120084000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>117020000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>115948000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>114636000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>112327000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>110706000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>89921000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>92073000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>89578000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>89180000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>86861000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7094,8 +7254,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7213,8 +7374,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7332,8 +7496,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7353,7 +7520,7 @@
         <v>6000</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -7451,8 +7618,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7570,127 +7740,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17162000</v>
+      </c>
+      <c r="E72" s="3">
         <v>17252000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9118000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14542000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15239000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15362000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19299000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>25469000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>26908000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27251000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>27274000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>28910000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>29059000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>29473000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>30107000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>33382000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>33189000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>34408000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>38551000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>38660000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>38073000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>38610000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>47029000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>47478000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>49854000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>50644000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>53986000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>52819000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>58090000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>55941000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>54666000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>52303000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>52095000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>49618000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>44052000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>42222000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>42165000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>40714000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>40641000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7808,8 +7984,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7927,8 +8106,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8046,127 +8228,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5981000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5448000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-8256000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-3301000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-3331000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-3914000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-23552000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-17976000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-17009000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-17233000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-16729000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-15517000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-15508000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-15883000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-17699000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-14888000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-15398000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-14999000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-14440000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-16682000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-18058000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-18316000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-11821000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-11667000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-9665000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-8617000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-4116000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-5322000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>125000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>339000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-1289000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-1441000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1222000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1656000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1086000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>-2037000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>95000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>817000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>2089000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8284,251 +8472,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E81" s="3">
         <v>8220000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5337000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-611000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-37000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3865000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6170000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1439000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-343000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-23000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1636000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-149000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-414000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-629000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3275000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>193000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1219000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4143000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-109000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>587000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-537000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8420000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-449000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2376000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-628000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1010000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1166000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2147000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3422000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2361000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2196000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2474000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3318000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1808000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1749000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1577000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>2276000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8570,127 +8767,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>466000</v>
+      </c>
+      <c r="E83" s="3">
         <v>286000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>444000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>441000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>442000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>246000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>467000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>456000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>457000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>261000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>493000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>498000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>486000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>502000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>493000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>498000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>486000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>534000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>523000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>551000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>536000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>578000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>565000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>547000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>556000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>628000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>576000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>546000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>521000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>583000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>523000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>507000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>501000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>582000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>522000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>494000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>471000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>546000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>474000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8808,8 +9009,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8927,8 +9131,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9046,8 +9253,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9165,8 +9375,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9284,127 +9497,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-179000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1331000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1123000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>227000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1616000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3450000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1345000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3923000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3362000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3381000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>22000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2875000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-318000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3457000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3190000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>81000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3216000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>716000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-262000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-483000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3387000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4009000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4819000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-5280000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4302000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2220000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2424000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-590000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2788000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2947000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4559000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4680000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3136000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2903000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3396000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>4949000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>2098000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>2832000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3202000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9446,127 +9665,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1275000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-956000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-885000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-427000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-674000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-648000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-611000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-404000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-567000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-431000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-332000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-296000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-468000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-326000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-284000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-263000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-349000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-222000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-245000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-222000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-291000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-265000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-262000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-348000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-428000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-447000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-465000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-421000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-501000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-495000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-457000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-376000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-394000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-435000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-399000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-439000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-932000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-599000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-595000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9684,8 +9907,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9803,127 +10029,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>5711000</v>
+      </c>
+      <c r="E94" s="3">
         <v>6400000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1955000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2229000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12626000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>679000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2100000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2074000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2804000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-403000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3015000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1823000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2151000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>290000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>3266000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2965000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1935000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>2966000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1659000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>2764000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1543000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4137000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-12307000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-379000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>517000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1194000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-86000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-767000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2424000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-902000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1414000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>119000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-457000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-218000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1123000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-260000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1416000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-614000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9965,8 +10197,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10006,8 +10239,8 @@
       <c r="O96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10040,52 +10273,55 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1158000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1157000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-1156000</v>
       </c>
       <c r="AD96" s="3">
         <v>-1156000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-1156000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1161000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-970000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-979000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-991000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-842000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-855000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-852000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-868000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-672000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-676000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10203,8 +10439,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10322,8 +10561,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10441,361 +10683,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7028000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2951000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-87000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-387000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-338000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>19971000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>10000000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4462000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-356000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-38000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3413000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1680000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-250000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-18000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-602000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-396000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4362000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1171000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-19000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-48000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2681000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-468000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>22462000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>10280000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1403000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4240000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2919000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2823000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-856000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3689000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-4332000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2845000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2241000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-3335000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-3311000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2463000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1574000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-2204000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-55000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>33000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-28000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>52000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-24000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>10000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>61000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-63000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-68000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>61000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-63000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-68000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-20000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-18000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>59000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>37000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>36000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-47000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>22000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-44000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>7000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>21000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>32000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>20000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-27000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1495000</v>
+      </c>
+      <c r="E102" s="3">
         <v>4781000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-914000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2367000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3659000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3840000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-933000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3980000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5778000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5881000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-443000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3811000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1117000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3399000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2677000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-650000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1716000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1513000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1161000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-689000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2812000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-9387000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4911000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5552000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-278000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>597000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2240000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-801000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-349000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-33000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1110000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>418000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>212000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-136000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>547000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-605000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-185000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>381000</v>
       </c>
     </row>
